--- a/research/traditional_assets/database/data/chile/chile_household_products.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0827426195576268</v>
+        <v>0.08255206448482122</v>
       </c>
       <c r="C2">
-        <v>50.88636865438254</v>
+        <v>50.55915697136617</v>
       </c>
       <c r="D2">
-        <v>49.52636865438254</v>
+        <v>49.78315697136618</v>
       </c>
       <c r="E2">
-        <v>-30.6</v>
+        <v>-30.016</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5840000000000001</v>
       </c>
       <c r="G2">
         <v>1.36</v>
@@ -1451,28 +1451,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0293752</v>
       </c>
       <c r="N2">
-        <v>8.893333333333334</v>
+        <v>8.863958133333334</v>
       </c>
       <c r="O2">
-        <v>2.401200000000001</v>
+        <v>2.393268696</v>
       </c>
       <c r="P2">
-        <v>6.492133333333333</v>
+        <v>6.470689437333334</v>
       </c>
       <c r="Q2">
-        <v>12.33213333333333</v>
+        <v>12.31068943733333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0827426195576268</v>
+        <v>0.08301502473214264</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.681606247346047</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>302.749711775012</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08255206448482122</v>
+        <v>0.08236150941201563</v>
       </c>
       <c r="C3">
-        <v>50.55915697136617</v>
+        <v>50.23462200040169</v>
       </c>
       <c r="D3">
-        <v>49.78315697136618</v>
+        <v>50.04262200040169</v>
       </c>
       <c r="E3">
-        <v>-30.016</v>
+        <v>-29.432</v>
       </c>
       <c r="F3">
-        <v>0.5840000000000001</v>
+        <v>1.168</v>
       </c>
       <c r="G3">
         <v>1.36</v>
@@ -1533,28 +1533,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M3">
-        <v>0.0293752</v>
+        <v>0.0587504</v>
       </c>
       <c r="N3">
-        <v>8.863958133333334</v>
+        <v>8.834582933333335</v>
       </c>
       <c r="O3">
-        <v>2.393268696</v>
+        <v>2.385337392000001</v>
       </c>
       <c r="P3">
-        <v>6.470689437333334</v>
+        <v>6.449245541333335</v>
       </c>
       <c r="Q3">
-        <v>12.31068943733333</v>
+        <v>12.28924554133333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08301502473214264</v>
+        <v>0.08329298919593431</v>
       </c>
       <c r="T3">
-        <v>0.681606247346047</v>
+        <v>0.686697264117479</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>302.749711775012</v>
+        <v>151.374855887506</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08236150941201563</v>
+        <v>0.08217095433921003</v>
       </c>
       <c r="C4">
-        <v>50.23462200040169</v>
+        <v>49.91280581305985</v>
       </c>
       <c r="D4">
-        <v>50.04262200040169</v>
+        <v>50.30480581305985</v>
       </c>
       <c r="E4">
-        <v>-29.432</v>
+        <v>-28.848</v>
       </c>
       <c r="F4">
-        <v>1.168</v>
+        <v>1.752</v>
       </c>
       <c r="G4">
         <v>1.36</v>
@@ -1615,28 +1615,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M4">
-        <v>0.0587504</v>
+        <v>0.0881256</v>
       </c>
       <c r="N4">
-        <v>8.834582933333335</v>
+        <v>8.805207733333335</v>
       </c>
       <c r="O4">
-        <v>2.385337392000001</v>
+        <v>2.377406088000001</v>
       </c>
       <c r="P4">
-        <v>6.449245541333335</v>
+        <v>6.427801645333334</v>
       </c>
       <c r="Q4">
-        <v>12.28924554133333</v>
+        <v>12.26780164533333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08329298919593431</v>
+        <v>0.08357668488578354</v>
       </c>
       <c r="T4">
-        <v>0.686697264117479</v>
+        <v>0.6918932503068786</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>151.374855887506</v>
+        <v>100.9165705916707</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08217095433921003</v>
+        <v>0.08198039926640444</v>
       </c>
       <c r="C5">
-        <v>49.91280581305985</v>
+        <v>49.59375136724228</v>
       </c>
       <c r="D5">
-        <v>50.30480581305985</v>
+        <v>50.56975136724228</v>
       </c>
       <c r="E5">
-        <v>-28.848</v>
+        <v>-28.264</v>
       </c>
       <c r="F5">
-        <v>1.752</v>
+        <v>2.336</v>
       </c>
       <c r="G5">
         <v>1.36</v>
@@ -1697,28 +1697,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M5">
-        <v>0.0881256</v>
+        <v>0.1175008</v>
       </c>
       <c r="N5">
-        <v>8.805207733333335</v>
+        <v>8.775832533333334</v>
       </c>
       <c r="O5">
-        <v>2.377406088000001</v>
+        <v>2.369474784</v>
       </c>
       <c r="P5">
-        <v>6.427801645333334</v>
+        <v>6.406357749333334</v>
       </c>
       <c r="Q5">
-        <v>12.26780164533333</v>
+        <v>12.24635774933333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08357668488578354</v>
+        <v>0.08386629090250462</v>
       </c>
       <c r="T5">
-        <v>0.6918932503068786</v>
+        <v>0.6971974862085576</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>100.9165705916707</v>
+        <v>75.68742794375301</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08198039926640444</v>
+        <v>0.08178984419359883</v>
       </c>
       <c r="C6">
-        <v>49.59375136724228</v>
+        <v>49.27750253064575</v>
       </c>
       <c r="D6">
-        <v>50.56975136724228</v>
+        <v>50.83750253064575</v>
       </c>
       <c r="E6">
-        <v>-28.264</v>
+        <v>-27.68</v>
       </c>
       <c r="F6">
-        <v>2.336</v>
+        <v>2.92</v>
       </c>
       <c r="G6">
         <v>1.36</v>
@@ -1779,28 +1779,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M6">
-        <v>0.1175008</v>
+        <v>0.146876</v>
       </c>
       <c r="N6">
-        <v>8.775832533333334</v>
+        <v>8.746457333333334</v>
       </c>
       <c r="O6">
-        <v>2.369474784</v>
+        <v>2.36154348</v>
       </c>
       <c r="P6">
-        <v>6.406357749333334</v>
+        <v>6.384913853333334</v>
       </c>
       <c r="Q6">
-        <v>12.24635774933333</v>
+        <v>12.22491385333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08386629090250462</v>
+        <v>0.08416199388799878</v>
       </c>
       <c r="T6">
-        <v>0.6971974862085576</v>
+        <v>0.7026133902344821</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.68742794375301</v>
+        <v>60.54994235500241</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08178984419359883</v>
+        <v>0.08159928912079326</v>
       </c>
       <c r="C7">
-        <v>49.27750253064575</v>
+        <v>48.96410410497574</v>
       </c>
       <c r="D7">
-        <v>50.83750253064575</v>
+        <v>51.10810410497574</v>
       </c>
       <c r="E7">
-        <v>-27.68</v>
+        <v>-27.096</v>
       </c>
       <c r="F7">
-        <v>2.92</v>
+        <v>3.504</v>
       </c>
       <c r="G7">
         <v>1.36</v>
@@ -1861,28 +1861,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M7">
-        <v>0.146876</v>
+        <v>0.1762512</v>
       </c>
       <c r="N7">
-        <v>8.746457333333334</v>
+        <v>8.717082133333335</v>
       </c>
       <c r="O7">
-        <v>2.36154348</v>
+        <v>2.353612176000001</v>
       </c>
       <c r="P7">
-        <v>6.384913853333334</v>
+        <v>6.363469957333335</v>
       </c>
       <c r="Q7">
-        <v>12.22491385333333</v>
+        <v>12.20346995733333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08416199388799878</v>
+        <v>0.0844639884263758</v>
       </c>
       <c r="T7">
-        <v>0.7026133902344821</v>
+        <v>0.7081445262609585</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.54994235500241</v>
+        <v>50.45828529583534</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08159928912079326</v>
+        <v>0.08140873404798765</v>
       </c>
       <c r="C8">
-        <v>48.96410410497574</v>
+        <v>48.6536018509376</v>
       </c>
       <c r="D8">
-        <v>51.10810410497574</v>
+        <v>51.3816018509376</v>
       </c>
       <c r="E8">
-        <v>-27.096</v>
+        <v>-26.512</v>
       </c>
       <c r="F8">
-        <v>3.504</v>
+        <v>4.088</v>
       </c>
       <c r="G8">
         <v>1.36</v>
@@ -1943,28 +1943,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M8">
-        <v>0.1762512</v>
+        <v>0.2056264</v>
       </c>
       <c r="N8">
-        <v>8.717082133333335</v>
+        <v>8.687706933333335</v>
       </c>
       <c r="O8">
-        <v>2.353612176000001</v>
+        <v>2.345680872</v>
       </c>
       <c r="P8">
-        <v>6.363469957333335</v>
+        <v>6.342026061333334</v>
       </c>
       <c r="Q8">
-        <v>12.20346995733333</v>
+        <v>12.18202606133333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0844639884263758</v>
+        <v>0.08477247747095447</v>
       </c>
       <c r="T8">
-        <v>0.7081445262609585</v>
+        <v>0.7137946114492945</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.45828529583535</v>
+        <v>43.24995882500173</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08140873404798765</v>
+        <v>0.08121817897518208</v>
       </c>
       <c r="C9">
-        <v>48.6536018509376</v>
+        <v>48.34604251403417</v>
       </c>
       <c r="D9">
-        <v>51.3816018509376</v>
+        <v>51.65804251403417</v>
       </c>
       <c r="E9">
-        <v>-26.512</v>
+        <v>-25.928</v>
       </c>
       <c r="F9">
-        <v>4.088000000000001</v>
+        <v>4.672000000000001</v>
       </c>
       <c r="G9">
         <v>1.36</v>
@@ -2025,28 +2025,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M9">
-        <v>0.2056264</v>
+        <v>0.2350016</v>
       </c>
       <c r="N9">
-        <v>8.687706933333335</v>
+        <v>8.658331733333334</v>
       </c>
       <c r="O9">
-        <v>2.345680872</v>
+        <v>2.337749568</v>
       </c>
       <c r="P9">
-        <v>6.342026061333334</v>
+        <v>6.320582165333334</v>
       </c>
       <c r="Q9">
-        <v>12.18202606133333</v>
+        <v>12.16058216533333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08477247747095447</v>
+        <v>0.08508767279911095</v>
       </c>
       <c r="T9">
-        <v>0.7137946114492945</v>
+        <v>0.7195675245765073</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.24995882500171</v>
+        <v>37.8437139718765</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08121817897518208</v>
+        <v>0.08102762390237647</v>
       </c>
       <c r="C10">
-        <v>48.34604251403417</v>
+        <v>48.04147385120115</v>
       </c>
       <c r="D10">
-        <v>51.65804251403417</v>
+        <v>51.93747385120115</v>
       </c>
       <c r="E10">
-        <v>-25.928</v>
+        <v>-25.344</v>
       </c>
       <c r="F10">
-        <v>4.672000000000001</v>
+        <v>5.256</v>
       </c>
       <c r="G10">
         <v>1.36</v>
@@ -2107,28 +2107,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M10">
-        <v>0.2350016</v>
+        <v>0.2643768</v>
       </c>
       <c r="N10">
-        <v>8.658331733333334</v>
+        <v>8.628956533333334</v>
       </c>
       <c r="O10">
-        <v>2.337749568</v>
+        <v>2.329818264</v>
       </c>
       <c r="P10">
-        <v>6.320582165333334</v>
+        <v>6.299138269333334</v>
       </c>
       <c r="Q10">
-        <v>12.16058216533333</v>
+        <v>12.13913826933333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08508767279911095</v>
+        <v>0.085409795497117</v>
       </c>
       <c r="T10">
-        <v>0.7195675245765073</v>
+        <v>0.7254673149153072</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.8437139718765</v>
+        <v>33.63885686389023</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08102762390237647</v>
+        <v>0.08083706882957088</v>
       </c>
       <c r="C11">
-        <v>48.04147385120115</v>
+        <v>47.73994465831106</v>
       </c>
       <c r="D11">
-        <v>51.93747385120115</v>
+        <v>52.21994465831106</v>
       </c>
       <c r="E11">
-        <v>-25.344</v>
+        <v>-24.76</v>
       </c>
       <c r="F11">
-        <v>5.256</v>
+        <v>5.84</v>
       </c>
       <c r="G11">
         <v>1.36</v>
@@ -2189,28 +2189,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M11">
-        <v>0.2643768</v>
+        <v>0.293752</v>
       </c>
       <c r="N11">
-        <v>8.628956533333334</v>
+        <v>8.599581333333335</v>
       </c>
       <c r="O11">
-        <v>2.329818264</v>
+        <v>2.32188696</v>
       </c>
       <c r="P11">
-        <v>6.299138269333334</v>
+        <v>6.277694373333334</v>
       </c>
       <c r="Q11">
-        <v>12.13913826933333</v>
+        <v>12.11769437333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.085409795497117</v>
+        <v>0.08573907647730097</v>
       </c>
       <c r="T11">
-        <v>0.7254673149153072</v>
+        <v>0.7314982117060805</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.63885686389023</v>
+        <v>30.27497117750121</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08083706882957088</v>
+        <v>0.08064651375676529</v>
       </c>
       <c r="C12">
-        <v>47.73994465831105</v>
+        <v>47.44150479858008</v>
       </c>
       <c r="D12">
-        <v>52.21994465831106</v>
+        <v>52.50550479858008</v>
       </c>
       <c r="E12">
-        <v>-24.76</v>
+        <v>-24.176</v>
       </c>
       <c r="F12">
-        <v>5.840000000000001</v>
+        <v>6.424</v>
       </c>
       <c r="G12">
         <v>1.36</v>
@@ -2271,28 +2271,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M12">
-        <v>0.293752</v>
+        <v>0.3231272</v>
       </c>
       <c r="N12">
-        <v>8.599581333333335</v>
+        <v>8.570206133333334</v>
       </c>
       <c r="O12">
-        <v>2.32188696</v>
+        <v>2.313955656000001</v>
       </c>
       <c r="P12">
-        <v>6.277694373333334</v>
+        <v>6.256250477333333</v>
       </c>
       <c r="Q12">
-        <v>12.11769437333333</v>
+        <v>12.09625047733333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08573907647730097</v>
+        <v>0.08607575703007336</v>
       </c>
       <c r="T12">
-        <v>0.7314982117060805</v>
+        <v>0.737664634267433</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.27497117750121</v>
+        <v>27.52270107045564</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08064651375676529</v>
+        <v>0.0804559586839597</v>
       </c>
       <c r="C13">
-        <v>47.44150479858008</v>
+        <v>47.14620523191187</v>
       </c>
       <c r="D13">
-        <v>52.50550479858008</v>
+        <v>52.79420523191187</v>
       </c>
       <c r="E13">
-        <v>-24.176</v>
+        <v>-23.592</v>
       </c>
       <c r="F13">
-        <v>6.424</v>
+        <v>7.008</v>
       </c>
       <c r="G13">
         <v>1.36</v>
@@ -2353,28 +2353,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M13">
-        <v>0.3231272</v>
+        <v>0.3525024</v>
       </c>
       <c r="N13">
-        <v>8.570206133333334</v>
+        <v>8.540830933333334</v>
       </c>
       <c r="O13">
-        <v>2.313955656000001</v>
+        <v>2.306024352</v>
       </c>
       <c r="P13">
-        <v>6.256250477333333</v>
+        <v>6.234806581333334</v>
       </c>
       <c r="Q13">
-        <v>12.09625047733333</v>
+        <v>12.07480658133333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08607575703007336</v>
+        <v>0.08642008941359057</v>
       </c>
       <c r="T13">
-        <v>0.737664634267433</v>
+        <v>0.743971202796089</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.52270107045564</v>
+        <v>25.22914264791767</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0804559586839597</v>
+        <v>0.08026540361115411</v>
       </c>
       <c r="C14">
-        <v>47.14620523191187</v>
+        <v>46.85409804521479</v>
       </c>
       <c r="D14">
-        <v>52.79420523191187</v>
+        <v>53.08609804521479</v>
       </c>
       <c r="E14">
-        <v>-23.592</v>
+        <v>-23.008</v>
       </c>
       <c r="F14">
-        <v>7.008</v>
+        <v>7.592000000000001</v>
       </c>
       <c r="G14">
         <v>1.36</v>
@@ -2435,28 +2435,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M14">
-        <v>0.3525024</v>
+        <v>0.3818776</v>
       </c>
       <c r="N14">
-        <v>8.540830933333334</v>
+        <v>8.511455733333335</v>
       </c>
       <c r="O14">
-        <v>2.306024352</v>
+        <v>2.298093048000001</v>
       </c>
       <c r="P14">
-        <v>6.234806581333334</v>
+        <v>6.213362685333335</v>
       </c>
       <c r="Q14">
-        <v>12.07480658133333</v>
+        <v>12.05336268533333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08642008941359057</v>
+        <v>0.08677233748408518</v>
       </c>
       <c r="T14">
-        <v>0.743971202796089</v>
+        <v>0.7504227499116105</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.22914264791767</v>
+        <v>23.28843936730862</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08026540361115411</v>
+        <v>0.08007484853834852</v>
       </c>
       <c r="C15">
-        <v>46.85409804521479</v>
+        <v>46.56523648373049</v>
       </c>
       <c r="D15">
-        <v>53.08609804521479</v>
+        <v>53.3812364837305</v>
       </c>
       <c r="E15">
-        <v>-23.008</v>
+        <v>-22.424</v>
       </c>
       <c r="F15">
-        <v>7.592000000000001</v>
+        <v>8.176000000000002</v>
       </c>
       <c r="G15">
         <v>1.36</v>
@@ -2517,28 +2517,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M15">
-        <v>0.3818776</v>
+        <v>0.4112528000000001</v>
       </c>
       <c r="N15">
-        <v>8.511455733333335</v>
+        <v>8.482080533333335</v>
       </c>
       <c r="O15">
-        <v>2.298093048000001</v>
+        <v>2.290161744000001</v>
       </c>
       <c r="P15">
-        <v>6.213362685333335</v>
+        <v>6.191918789333334</v>
       </c>
       <c r="Q15">
-        <v>12.05336268533333</v>
+        <v>12.03191878933333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08677233748408518</v>
+        <v>0.08713277737017269</v>
       </c>
       <c r="T15">
-        <v>0.7504227499116105</v>
+        <v>0.7570243330065628</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.28843936730862</v>
+        <v>21.62497941250086</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08007484853834852</v>
+        <v>0.07988429346554292</v>
       </c>
       <c r="C16">
-        <v>46.56523648373049</v>
+        <v>46.27967498341346</v>
       </c>
       <c r="D16">
-        <v>53.3812364837305</v>
+        <v>53.67967498341346</v>
       </c>
       <c r="E16">
-        <v>-22.424</v>
+        <v>-21.84</v>
       </c>
       <c r="F16">
-        <v>8.176000000000002</v>
+        <v>8.760000000000002</v>
       </c>
       <c r="G16">
         <v>1.36</v>
@@ -2599,28 +2599,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M16">
-        <v>0.4112528000000001</v>
+        <v>0.4406280000000001</v>
       </c>
       <c r="N16">
-        <v>8.482080533333335</v>
+        <v>8.452705333333334</v>
       </c>
       <c r="O16">
-        <v>2.290161744000001</v>
+        <v>2.28223044</v>
       </c>
       <c r="P16">
-        <v>6.191918789333334</v>
+        <v>6.170474893333334</v>
       </c>
       <c r="Q16">
-        <v>12.03191878933333</v>
+        <v>12.01047489333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08713277737017269</v>
+        <v>0.08750169819475638</v>
       </c>
       <c r="T16">
-        <v>0.7570243330065628</v>
+        <v>0.7637812474684552</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.62497941250086</v>
+        <v>20.18331411833413</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07988429346554292</v>
+        <v>0.07969373839273733</v>
       </c>
       <c r="C17">
-        <v>46.27967498341346</v>
+        <v>45.99746920440256</v>
       </c>
       <c r="D17">
-        <v>53.67967498341346</v>
+        <v>53.98146920440256</v>
       </c>
       <c r="E17">
-        <v>-21.84</v>
+        <v>-21.256</v>
       </c>
       <c r="F17">
-        <v>8.76</v>
+        <v>9.344000000000001</v>
       </c>
       <c r="G17">
         <v>1.36</v>
@@ -2681,28 +2681,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M17">
-        <v>0.440628</v>
+        <v>0.4700032</v>
       </c>
       <c r="N17">
-        <v>8.452705333333334</v>
+        <v>8.423330133333334</v>
       </c>
       <c r="O17">
-        <v>2.28223044</v>
+        <v>2.274299136</v>
       </c>
       <c r="P17">
-        <v>6.170474893333334</v>
+        <v>6.149030997333334</v>
       </c>
       <c r="Q17">
-        <v>12.01047489333333</v>
+        <v>11.98903099733333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08750169819475638</v>
+        <v>0.08787940284849682</v>
       </c>
       <c r="T17">
-        <v>0.7637812474684552</v>
+        <v>0.7706990408461069</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.18331411833414</v>
+        <v>18.92185698593825</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07969373839273733</v>
+        <v>0.07950318331993174</v>
       </c>
       <c r="C18">
-        <v>45.99746920440256</v>
+        <v>45.71867606562846</v>
       </c>
       <c r="D18">
-        <v>53.98146920440256</v>
+        <v>54.28667606562846</v>
       </c>
       <c r="E18">
-        <v>-21.256</v>
+        <v>-20.672</v>
       </c>
       <c r="F18">
-        <v>9.344000000000001</v>
+        <v>9.928000000000001</v>
       </c>
       <c r="G18">
         <v>1.36</v>
@@ -2763,28 +2763,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M18">
-        <v>0.4700032</v>
+        <v>0.4993784</v>
       </c>
       <c r="N18">
-        <v>8.423330133333334</v>
+        <v>8.393954933333335</v>
       </c>
       <c r="O18">
-        <v>2.274299136</v>
+        <v>2.266367832000001</v>
       </c>
       <c r="P18">
-        <v>6.149030997333334</v>
+        <v>6.127587101333335</v>
       </c>
       <c r="Q18">
-        <v>11.98903099733333</v>
+        <v>11.96758710133333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08787940284849682</v>
+        <v>0.08826620881919486</v>
       </c>
       <c r="T18">
-        <v>0.7706990408461069</v>
+        <v>0.7777835280400875</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.92185698593825</v>
+        <v>17.80880657500071</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07950318331993174</v>
+        <v>0.07931262824712614</v>
       </c>
       <c r="C19">
-        <v>45.71867606562846</v>
+        <v>45.44335378060139</v>
       </c>
       <c r="D19">
-        <v>54.28667606562846</v>
+        <v>54.59535378060139</v>
       </c>
       <c r="E19">
-        <v>-20.672</v>
+        <v>-20.088</v>
       </c>
       <c r="F19">
-        <v>9.928000000000001</v>
+        <v>10.512</v>
       </c>
       <c r="G19">
         <v>1.36</v>
@@ -2845,28 +2845,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M19">
-        <v>0.4993784</v>
+        <v>0.5287536</v>
       </c>
       <c r="N19">
-        <v>8.393954933333335</v>
+        <v>8.364579733333334</v>
       </c>
       <c r="O19">
-        <v>2.266367832000001</v>
+        <v>2.258436528</v>
       </c>
       <c r="P19">
-        <v>6.127587101333335</v>
+        <v>6.106143205333334</v>
       </c>
       <c r="Q19">
-        <v>11.96758710133333</v>
+        <v>11.94614320533333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08826620881919486</v>
+        <v>0.08866244908186115</v>
       </c>
       <c r="T19">
-        <v>0.7777835280400875</v>
+        <v>0.785040807604653</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.80880657500071</v>
+        <v>16.81942843194511</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07931262824712615</v>
+        <v>0.07912207317432056</v>
       </c>
       <c r="C20">
-        <v>45.44335378060137</v>
+        <v>45.17156189442685</v>
       </c>
       <c r="D20">
-        <v>54.59535378060137</v>
+        <v>54.90756189442686</v>
       </c>
       <c r="E20">
-        <v>-20.088</v>
+        <v>-19.504</v>
       </c>
       <c r="F20">
-        <v>10.512</v>
+        <v>11.096</v>
       </c>
       <c r="G20">
         <v>1.36</v>
@@ -2927,28 +2927,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M20">
-        <v>0.5287536</v>
+        <v>0.5581288000000001</v>
       </c>
       <c r="N20">
-        <v>8.364579733333334</v>
+        <v>8.335204533333334</v>
       </c>
       <c r="O20">
-        <v>2.258436528</v>
+        <v>2.250505224</v>
       </c>
       <c r="P20">
-        <v>6.106143205333334</v>
+        <v>6.084699309333334</v>
       </c>
       <c r="Q20">
-        <v>11.94614320533333</v>
+        <v>11.92469930933333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08866244908186115</v>
+        <v>0.08906847305471674</v>
       </c>
       <c r="T20">
-        <v>0.785040807604653</v>
+        <v>0.7924772792572327</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.81942843194511</v>
+        <v>15.93419535657958</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07912207317432056</v>
+        <v>0.07893151810151497</v>
       </c>
       <c r="C21">
-        <v>45.17156189442685</v>
+        <v>44.90336132209907</v>
       </c>
       <c r="D21">
-        <v>54.90756189442686</v>
+        <v>55.22336132209907</v>
       </c>
       <c r="E21">
-        <v>-19.504</v>
+        <v>-18.92</v>
       </c>
       <c r="F21">
-        <v>11.096</v>
+        <v>11.68</v>
       </c>
       <c r="G21">
         <v>1.36</v>
@@ -3009,28 +3009,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M21">
-        <v>0.5581288000000001</v>
+        <v>0.587504</v>
       </c>
       <c r="N21">
-        <v>8.335204533333334</v>
+        <v>8.305829333333335</v>
       </c>
       <c r="O21">
-        <v>2.250505224</v>
+        <v>2.242573920000001</v>
       </c>
       <c r="P21">
-        <v>6.084699309333334</v>
+        <v>6.063255413333335</v>
       </c>
       <c r="Q21">
-        <v>11.92469930933333</v>
+        <v>11.90325541333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08906847305471674</v>
+        <v>0.0894846476268937</v>
       </c>
       <c r="T21">
-        <v>0.7924772792572327</v>
+        <v>0.8000996627011266</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.93419535657958</v>
+        <v>15.1374855887506</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07893151810151497</v>
+        <v>0.07874096302870937</v>
       </c>
       <c r="C22">
-        <v>44.90336132209907</v>
+        <v>44.63881438812302</v>
       </c>
       <c r="D22">
-        <v>55.22336132209907</v>
+        <v>55.54281438812302</v>
       </c>
       <c r="E22">
-        <v>-18.92</v>
+        <v>-18.336</v>
       </c>
       <c r="F22">
-        <v>11.68</v>
+        <v>12.264</v>
       </c>
       <c r="G22">
         <v>1.36</v>
@@ -3091,28 +3091,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M22">
-        <v>0.587504</v>
+        <v>0.6168792000000001</v>
       </c>
       <c r="N22">
-        <v>8.305829333333335</v>
+        <v>8.276454133333335</v>
       </c>
       <c r="O22">
-        <v>2.242573920000001</v>
+        <v>2.234642616</v>
       </c>
       <c r="P22">
-        <v>6.063255413333335</v>
+        <v>6.041811517333334</v>
       </c>
       <c r="Q22">
-        <v>11.90325541333333</v>
+        <v>11.88181151733333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0894846476268937</v>
+        <v>0.08991135826418907</v>
       </c>
       <c r="T22">
-        <v>0.8000996627011266</v>
+        <v>0.8079150178777774</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.1374855887506</v>
+        <v>14.41665294166724</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07874096302870937</v>
+        <v>0.07855040795590378</v>
       </c>
       <c r="C23">
-        <v>44.63881438812302</v>
+        <v>44.37798486752</v>
       </c>
       <c r="D23">
-        <v>55.54281438812302</v>
+        <v>55.86598486752</v>
       </c>
       <c r="E23">
-        <v>-18.336</v>
+        <v>-17.752</v>
       </c>
       <c r="F23">
-        <v>12.264</v>
+        <v>12.848</v>
       </c>
       <c r="G23">
         <v>1.36</v>
@@ -3173,28 +3173,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M23">
-        <v>0.6168792000000001</v>
+        <v>0.6462544</v>
       </c>
       <c r="N23">
-        <v>8.276454133333335</v>
+        <v>8.247078933333334</v>
       </c>
       <c r="O23">
-        <v>2.234642616</v>
+        <v>2.226711312</v>
       </c>
       <c r="P23">
-        <v>6.041811517333334</v>
+        <v>6.020367621333333</v>
       </c>
       <c r="Q23">
-        <v>11.88181151733333</v>
+        <v>11.86036762133333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08991135826418907</v>
+        <v>0.09034901019987662</v>
       </c>
       <c r="T23">
-        <v>0.8079150178777774</v>
+        <v>0.8159307667769065</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.41665294166724</v>
+        <v>13.76135053522782</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07855040795590378</v>
+        <v>0.07835985288309819</v>
       </c>
       <c r="C24">
-        <v>44.37798486752</v>
+        <v>44.12093802827314</v>
       </c>
       <c r="D24">
-        <v>55.86598486752</v>
+        <v>56.19293802827314</v>
       </c>
       <c r="E24">
-        <v>-17.752</v>
+        <v>-17.168</v>
       </c>
       <c r="F24">
-        <v>12.848</v>
+        <v>13.432</v>
       </c>
       <c r="G24">
         <v>1.36</v>
@@ -3255,28 +3255,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M24">
-        <v>0.6462544</v>
+        <v>0.6756296000000001</v>
       </c>
       <c r="N24">
-        <v>8.247078933333334</v>
+        <v>8.217703733333334</v>
       </c>
       <c r="O24">
-        <v>2.226711312</v>
+        <v>2.218780008</v>
       </c>
       <c r="P24">
-        <v>6.020367621333333</v>
+        <v>5.998923725333333</v>
       </c>
       <c r="Q24">
-        <v>11.86036762133333</v>
+        <v>11.83892372533333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09034901019987662</v>
+        <v>0.09079802971830933</v>
       </c>
       <c r="T24">
-        <v>0.8159307667769065</v>
+        <v>0.8241547169461427</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.76135053522782</v>
+        <v>13.16303094673965</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07835985288309819</v>
+        <v>0.07843209781029259</v>
       </c>
       <c r="C25">
-        <v>44.12093802827314</v>
+        <v>43.4125312328445</v>
       </c>
       <c r="D25">
-        <v>56.19293802827314</v>
+        <v>56.06853123284451</v>
       </c>
       <c r="E25">
-        <v>-17.168</v>
+        <v>-16.584</v>
       </c>
       <c r="F25">
-        <v>13.432</v>
+        <v>14.016</v>
       </c>
       <c r="G25">
         <v>1.36</v>
@@ -3337,45 +3337,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M25">
-        <v>0.6756296000000001</v>
+        <v>0.7260288</v>
       </c>
       <c r="N25">
-        <v>8.217703733333334</v>
+        <v>8.167304533333335</v>
       </c>
       <c r="O25">
-        <v>2.218780008</v>
+        <v>2.205172224</v>
       </c>
       <c r="P25">
-        <v>5.998923725333333</v>
+        <v>5.962132309333334</v>
       </c>
       <c r="Q25">
-        <v>11.83892372533333</v>
+        <v>11.80213230933333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09079802971830933</v>
+        <v>0.09125886553985867</v>
       </c>
       <c r="T25">
-        <v>0.8241547169461427</v>
+        <v>0.8325950868566747</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.16303094673965</v>
+        <v>12.24928450955848</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07843209781029259</v>
+        <v>0.07825249273748699</v>
       </c>
       <c r="C26">
-        <v>43.41253123284451</v>
+        <v>43.13883690691512</v>
       </c>
       <c r="D26">
-        <v>56.06853123284451</v>
+        <v>56.37883690691513</v>
       </c>
       <c r="E26">
-        <v>-16.584</v>
+        <v>-16</v>
       </c>
       <c r="F26">
-        <v>14.016</v>
+        <v>14.6</v>
       </c>
       <c r="G26">
         <v>1.36</v>
@@ -3419,28 +3419,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M26">
-        <v>0.7260288</v>
+        <v>0.7562800000000001</v>
       </c>
       <c r="N26">
-        <v>8.167304533333335</v>
+        <v>8.137053333333334</v>
       </c>
       <c r="O26">
-        <v>2.205172224</v>
+        <v>2.1970044</v>
       </c>
       <c r="P26">
-        <v>5.962132309333334</v>
+        <v>5.940048933333333</v>
       </c>
       <c r="Q26">
-        <v>11.80213230933333</v>
+        <v>11.78004893333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09125886553985867</v>
+        <v>0.09173199031664933</v>
       </c>
       <c r="T26">
-        <v>0.8325950868566747</v>
+        <v>0.8412605332981543</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.24928450955848</v>
+        <v>11.75931312917614</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07825249273748699</v>
+        <v>0.0780728876646814</v>
       </c>
       <c r="C27">
-        <v>43.13883690691512</v>
+        <v>42.86859640722915</v>
       </c>
       <c r="D27">
-        <v>56.37883690691513</v>
+        <v>56.69259640722915</v>
       </c>
       <c r="E27">
-        <v>-16</v>
+        <v>-15.416</v>
       </c>
       <c r="F27">
-        <v>14.6</v>
+        <v>15.184</v>
       </c>
       <c r="G27">
         <v>1.36</v>
@@ -3501,28 +3501,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M27">
-        <v>0.7562800000000001</v>
+        <v>0.7865312000000001</v>
       </c>
       <c r="N27">
-        <v>8.137053333333334</v>
+        <v>8.106802133333334</v>
       </c>
       <c r="O27">
-        <v>2.1970044</v>
+        <v>2.188836576</v>
       </c>
       <c r="P27">
-        <v>5.940048933333333</v>
+        <v>5.917965557333334</v>
       </c>
       <c r="Q27">
-        <v>11.78004893333333</v>
+        <v>11.75796555733333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09173199031664933</v>
+        <v>0.09221790224956947</v>
       </c>
       <c r="T27">
-        <v>0.8412605332981543</v>
+        <v>0.8501601809948088</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.75931312917614</v>
+        <v>11.30703185497706</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0780728876646814</v>
+        <v>0.07789328259187581</v>
       </c>
       <c r="C28">
-        <v>42.86859640722915</v>
+        <v>42.60186772019345</v>
       </c>
       <c r="D28">
-        <v>56.69259640722915</v>
+        <v>57.00986772019345</v>
       </c>
       <c r="E28">
-        <v>-15.416</v>
+        <v>-14.832</v>
       </c>
       <c r="F28">
-        <v>15.184</v>
+        <v>15.768</v>
       </c>
       <c r="G28">
         <v>1.36</v>
@@ -3583,28 +3583,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M28">
-        <v>0.7865312000000001</v>
+        <v>0.8167824000000001</v>
       </c>
       <c r="N28">
-        <v>8.106802133333334</v>
+        <v>8.076550933333333</v>
       </c>
       <c r="O28">
-        <v>2.188836576</v>
+        <v>2.180668752</v>
       </c>
       <c r="P28">
-        <v>5.917965557333334</v>
+        <v>5.895882181333333</v>
       </c>
       <c r="Q28">
-        <v>11.75796555733333</v>
+        <v>11.73588218133333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09221790224956947</v>
+        <v>0.09271712683818603</v>
       </c>
       <c r="T28">
-        <v>0.8501601809948088</v>
+        <v>0.8593036546557554</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.30703185497706</v>
+        <v>10.88825289738532</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07789328259187581</v>
+        <v>0.07771367751907021</v>
       </c>
       <c r="C29">
-        <v>42.60186772019345</v>
+        <v>42.33871013756776</v>
       </c>
       <c r="D29">
-        <v>57.00986772019345</v>
+        <v>57.33071013756776</v>
       </c>
       <c r="E29">
-        <v>-14.832</v>
+        <v>-14.248</v>
       </c>
       <c r="F29">
-        <v>15.768</v>
+        <v>16.352</v>
       </c>
       <c r="G29">
         <v>1.36</v>
@@ -3665,28 +3665,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M29">
-        <v>0.8167824000000001</v>
+        <v>0.8470336000000002</v>
       </c>
       <c r="N29">
-        <v>8.076550933333333</v>
+        <v>8.046299733333335</v>
       </c>
       <c r="O29">
-        <v>2.180668752</v>
+        <v>2.172500928000001</v>
       </c>
       <c r="P29">
-        <v>5.895882181333333</v>
+        <v>5.873798805333334</v>
       </c>
       <c r="Q29">
-        <v>11.73588218133333</v>
+        <v>11.71379880533333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09271712683818603</v>
+        <v>0.09323021877648641</v>
       </c>
       <c r="T29">
-        <v>0.8593036546557554</v>
+        <v>0.8687011136961726</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.88825289738532</v>
+        <v>10.4993867224787</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07771367751907021</v>
+        <v>0.07753407244626462</v>
       </c>
       <c r="C30">
-        <v>42.33871013756776</v>
+        <v>42.07918429340421</v>
       </c>
       <c r="D30">
-        <v>57.33071013756776</v>
+        <v>57.65518429340421</v>
       </c>
       <c r="E30">
-        <v>-14.248</v>
+        <v>-13.664</v>
       </c>
       <c r="F30">
-        <v>16.352</v>
+        <v>16.936</v>
       </c>
       <c r="G30">
         <v>1.36</v>
@@ -3747,28 +3747,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M30">
-        <v>0.8470336000000002</v>
+        <v>0.8772848000000002</v>
       </c>
       <c r="N30">
-        <v>8.046299733333335</v>
+        <v>8.016048533333334</v>
       </c>
       <c r="O30">
-        <v>2.172500928000001</v>
+        <v>2.164333104</v>
       </c>
       <c r="P30">
-        <v>5.873798805333334</v>
+        <v>5.851715429333334</v>
       </c>
       <c r="Q30">
-        <v>11.71379880533333</v>
+        <v>11.69171542933333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09323021877648641</v>
+        <v>0.09375776400882341</v>
       </c>
       <c r="T30">
-        <v>0.8687011136961726</v>
+        <v>0.8783632898926581</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.4993867224787</v>
+        <v>10.13733890446219</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07753407244626462</v>
+        <v>0.07772676737345903</v>
       </c>
       <c r="C31">
-        <v>42.07918429340421</v>
+        <v>41.1472047623154</v>
       </c>
       <c r="D31">
-        <v>57.65518429340421</v>
+        <v>57.30720476231539</v>
       </c>
       <c r="E31">
-        <v>-13.664</v>
+        <v>-13.08</v>
       </c>
       <c r="F31">
-        <v>16.936</v>
+        <v>17.52</v>
       </c>
       <c r="G31">
         <v>1.36</v>
@@ -3829,45 +3829,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M31">
-        <v>0.8772848</v>
+        <v>0.9373199999999999</v>
       </c>
       <c r="N31">
-        <v>8.016048533333334</v>
+        <v>7.956013333333335</v>
       </c>
       <c r="O31">
-        <v>2.164333104</v>
+        <v>2.1481236</v>
       </c>
       <c r="P31">
-        <v>5.851715429333334</v>
+        <v>5.807889733333335</v>
       </c>
       <c r="Q31">
-        <v>11.69171542933333</v>
+        <v>11.64788973333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09375776400882341</v>
+        <v>0.09430038196208433</v>
       </c>
       <c r="T31">
-        <v>0.8783632898926581</v>
+        <v>0.8883015282661859</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>10.13733890446219</v>
+        <v>9.488043926656143</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07772676737345903</v>
+        <v>0.07755957230065344</v>
       </c>
       <c r="C32">
-        <v>41.1472047623154</v>
+        <v>40.86489277567452</v>
       </c>
       <c r="D32">
-        <v>57.30720476231539</v>
+        <v>57.60889277567453</v>
       </c>
       <c r="E32">
-        <v>-13.08</v>
+        <v>-12.496</v>
       </c>
       <c r="F32">
-        <v>17.52</v>
+        <v>18.104</v>
       </c>
       <c r="G32">
         <v>1.36</v>
@@ -3911,28 +3911,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M32">
-        <v>0.9373199999999999</v>
+        <v>0.9685640000000001</v>
       </c>
       <c r="N32">
-        <v>7.956013333333335</v>
+        <v>7.924769333333335</v>
       </c>
       <c r="O32">
-        <v>2.1481236</v>
+        <v>2.13968772</v>
       </c>
       <c r="P32">
-        <v>5.807889733333335</v>
+        <v>5.785081613333334</v>
       </c>
       <c r="Q32">
-        <v>11.64788973333333</v>
+        <v>11.62508161333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09430038196208433</v>
+        <v>0.09485872797196152</v>
       </c>
       <c r="T32">
-        <v>0.8883015282661859</v>
+        <v>0.8985278315201058</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.488043926656143</v>
+        <v>9.181977993538201</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07755957230065344</v>
+        <v>0.07739237722784784</v>
       </c>
       <c r="C33">
-        <v>40.86489277567452</v>
+        <v>40.58577401181616</v>
       </c>
       <c r="D33">
-        <v>57.60889277567453</v>
+        <v>57.91377401181617</v>
       </c>
       <c r="E33">
-        <v>-12.496</v>
+        <v>-11.912</v>
       </c>
       <c r="F33">
-        <v>18.104</v>
+        <v>18.688</v>
       </c>
       <c r="G33">
         <v>1.36</v>
@@ -3993,28 +3993,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M33">
-        <v>0.9685640000000001</v>
+        <v>0.9998080000000001</v>
       </c>
       <c r="N33">
-        <v>7.924769333333335</v>
+        <v>7.893525333333335</v>
       </c>
       <c r="O33">
-        <v>2.13968772</v>
+        <v>2.13125184</v>
       </c>
       <c r="P33">
-        <v>5.785081613333334</v>
+        <v>5.762273493333334</v>
       </c>
       <c r="Q33">
-        <v>11.62508161333333</v>
+        <v>11.60227349333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09485872797196152</v>
+        <v>0.09543349592330566</v>
       </c>
       <c r="T33">
-        <v>0.8985278315201058</v>
+        <v>0.9090549083991409</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.181977993538201</v>
+        <v>8.895041181240131</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07739237722784784</v>
+        <v>0.07722518215504226</v>
       </c>
       <c r="C34">
-        <v>40.58577401181616</v>
+        <v>40.30989943857038</v>
       </c>
       <c r="D34">
-        <v>57.91377401181617</v>
+        <v>58.22189943857038</v>
       </c>
       <c r="E34">
-        <v>-11.912</v>
+        <v>-11.328</v>
       </c>
       <c r="F34">
-        <v>18.688</v>
+        <v>19.272</v>
       </c>
       <c r="G34">
         <v>1.36</v>
@@ -4075,28 +4075,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M34">
-        <v>0.9998080000000001</v>
+        <v>1.031052</v>
       </c>
       <c r="N34">
-        <v>7.893525333333335</v>
+        <v>7.862281333333335</v>
       </c>
       <c r="O34">
-        <v>2.13125184</v>
+        <v>2.122815960000001</v>
       </c>
       <c r="P34">
-        <v>5.762273493333334</v>
+        <v>5.739465373333334</v>
       </c>
       <c r="Q34">
-        <v>11.60227349333333</v>
+        <v>11.57946537333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09543349592330566</v>
+        <v>0.09602542112692874</v>
       </c>
       <c r="T34">
-        <v>0.9090549083991409</v>
+        <v>0.919896226379043</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.895041181240131</v>
+        <v>8.625494478778311</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07722518215504226</v>
+        <v>0.07705798708223667</v>
       </c>
       <c r="C35">
-        <v>40.30989943857038</v>
+        <v>40.03732111424966</v>
       </c>
       <c r="D35">
-        <v>58.22189943857038</v>
+        <v>58.53332111424966</v>
       </c>
       <c r="E35">
-        <v>-11.328</v>
+        <v>-10.744</v>
       </c>
       <c r="F35">
-        <v>19.272</v>
+        <v>19.856</v>
       </c>
       <c r="G35">
         <v>1.36</v>
@@ -4157,28 +4157,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M35">
-        <v>1.031052</v>
+        <v>1.062296</v>
       </c>
       <c r="N35">
-        <v>7.862281333333335</v>
+        <v>7.831037333333335</v>
       </c>
       <c r="O35">
-        <v>2.122815960000001</v>
+        <v>2.114380080000001</v>
       </c>
       <c r="P35">
-        <v>5.739465373333334</v>
+        <v>5.716657253333334</v>
       </c>
       <c r="Q35">
-        <v>11.57946537333333</v>
+        <v>11.55665725333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09602542112692874</v>
+        <v>0.09663528345793435</v>
       </c>
       <c r="T35">
-        <v>0.919896226379043</v>
+        <v>0.9310660691462146</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.625494478778311</v>
+        <v>8.371803464696594</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07705798708223667</v>
+        <v>0.07689079200943105</v>
       </c>
       <c r="C36">
-        <v>40.03732111424966</v>
+        <v>39.76809221696981</v>
       </c>
       <c r="D36">
-        <v>58.53332111424966</v>
+        <v>58.84809221696982</v>
       </c>
       <c r="E36">
-        <v>-10.744</v>
+        <v>-10.16</v>
       </c>
       <c r="F36">
-        <v>19.856</v>
+        <v>20.44</v>
       </c>
       <c r="G36">
         <v>1.36</v>
@@ -4239,28 +4239,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M36">
-        <v>1.062296</v>
+        <v>1.09354</v>
       </c>
       <c r="N36">
-        <v>7.831037333333335</v>
+        <v>7.799793333333334</v>
       </c>
       <c r="O36">
-        <v>2.114380080000001</v>
+        <v>2.105944200000001</v>
       </c>
       <c r="P36">
-        <v>5.716657253333334</v>
+        <v>5.693849133333334</v>
       </c>
       <c r="Q36">
-        <v>11.55665725333333</v>
+        <v>11.53384913333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09663528345793435</v>
+        <v>0.09726391078374011</v>
       </c>
       <c r="T36">
-        <v>0.9310660691462146</v>
+        <v>0.9425795993831454</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.371803464696594</v>
+        <v>8.132609079990978</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07689079200943105</v>
+        <v>0.07672359693662548</v>
       </c>
       <c r="C37">
-        <v>39.76809221696981</v>
+        <v>39.50226707492213</v>
       </c>
       <c r="D37">
-        <v>58.84809221696982</v>
+        <v>59.16626707492213</v>
       </c>
       <c r="E37">
-        <v>-10.16</v>
+        <v>-9.575999999999997</v>
       </c>
       <c r="F37">
-        <v>20.44</v>
+        <v>21.024</v>
       </c>
       <c r="G37">
         <v>1.36</v>
@@ -4321,28 +4321,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M37">
-        <v>1.09354</v>
+        <v>1.124784</v>
       </c>
       <c r="N37">
-        <v>7.799793333333334</v>
+        <v>7.768549333333334</v>
       </c>
       <c r="O37">
-        <v>2.105944200000001</v>
+        <v>2.097508320000001</v>
       </c>
       <c r="P37">
-        <v>5.693849133333334</v>
+        <v>5.671041013333333</v>
       </c>
       <c r="Q37">
-        <v>11.53384913333333</v>
+        <v>11.51104101333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09726391078374011</v>
+        <v>0.09791218271347732</v>
       </c>
       <c r="T37">
-        <v>0.9425795993831454</v>
+        <v>0.9544529274399803</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.132609079990978</v>
+        <v>7.906703272213449</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07672359693662548</v>
+        <v>0.07655640186381987</v>
       </c>
       <c r="C38">
-        <v>39.50226707492213</v>
+        <v>39.23990119763349</v>
       </c>
       <c r="D38">
-        <v>59.16626707492213</v>
+        <v>59.48790119763348</v>
       </c>
       <c r="E38">
-        <v>-9.576000000000001</v>
+        <v>-8.992000000000001</v>
       </c>
       <c r="F38">
-        <v>21.024</v>
+        <v>21.608</v>
       </c>
       <c r="G38">
         <v>1.36</v>
@@ -4403,28 +4403,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M38">
-        <v>1.124784</v>
+        <v>1.156028</v>
       </c>
       <c r="N38">
-        <v>7.768549333333334</v>
+        <v>7.737305333333334</v>
       </c>
       <c r="O38">
-        <v>2.097508320000001</v>
+        <v>2.08907244</v>
       </c>
       <c r="P38">
-        <v>5.671041013333333</v>
+        <v>5.648232893333335</v>
       </c>
       <c r="Q38">
-        <v>11.51104101333333</v>
+        <v>11.48823289333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09791218271347732</v>
+        <v>0.098581034704476</v>
       </c>
       <c r="T38">
-        <v>0.9544529274399803</v>
+        <v>0.9667031865462384</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.906703272213451</v>
+        <v>7.693008589180655</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07655640186381987</v>
+        <v>0.07661112679101428</v>
       </c>
       <c r="C39">
-        <v>39.23990119763349</v>
+        <v>38.55024225552241</v>
       </c>
       <c r="D39">
-        <v>59.48790119763348</v>
+        <v>59.38224225552241</v>
       </c>
       <c r="E39">
-        <v>-8.992000000000001</v>
+        <v>-8.407999999999998</v>
       </c>
       <c r="F39">
-        <v>21.608</v>
+        <v>22.192</v>
       </c>
       <c r="G39">
         <v>1.36</v>
@@ -4485,45 +4485,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M39">
-        <v>1.156028</v>
+        <v>1.2050256</v>
       </c>
       <c r="N39">
-        <v>7.737305333333334</v>
+        <v>7.688307733333335</v>
       </c>
       <c r="O39">
-        <v>2.08907244</v>
+        <v>2.075843088000001</v>
       </c>
       <c r="P39">
-        <v>5.648232893333335</v>
+        <v>5.612464645333334</v>
       </c>
       <c r="Q39">
-        <v>11.48823289333333</v>
+        <v>11.45246464533333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.098581034704476</v>
+        <v>0.09927146256615207</v>
       </c>
       <c r="T39">
-        <v>0.9667031865462384</v>
+        <v>0.9793486153010856</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.693008589180655</v>
+        <v>7.380202821693858</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07661112679101428</v>
+        <v>0.07644977171820869</v>
       </c>
       <c r="C40">
-        <v>38.55024225552241</v>
+        <v>38.27885880975295</v>
       </c>
       <c r="D40">
-        <v>59.38224225552241</v>
+        <v>59.69485880975296</v>
       </c>
       <c r="E40">
-        <v>-8.407999999999998</v>
+        <v>-7.823999999999998</v>
       </c>
       <c r="F40">
-        <v>22.192</v>
+        <v>22.776</v>
       </c>
       <c r="G40">
         <v>1.36</v>
@@ -4567,28 +4567,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M40">
-        <v>1.2050256</v>
+        <v>1.2367368</v>
       </c>
       <c r="N40">
-        <v>7.688307733333335</v>
+        <v>7.656596533333334</v>
       </c>
       <c r="O40">
-        <v>2.075843088000001</v>
+        <v>2.067281064</v>
       </c>
       <c r="P40">
-        <v>5.612464645333334</v>
+        <v>5.589315469333334</v>
       </c>
       <c r="Q40">
-        <v>11.45246464533333</v>
+        <v>11.42931546933333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09927146256615207</v>
+        <v>0.0999845274068995</v>
       </c>
       <c r="T40">
-        <v>0.9793486153010856</v>
+        <v>0.9924086482774034</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.380202821693858</v>
+        <v>7.190966851906834</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07644977171820869</v>
+        <v>0.07628841664540312</v>
       </c>
       <c r="C41">
-        <v>38.27885880975295</v>
+        <v>38.01078431029279</v>
       </c>
       <c r="D41">
-        <v>59.69485880975296</v>
+        <v>60.01078431029279</v>
       </c>
       <c r="E41">
-        <v>-7.823999999999998</v>
+        <v>-7.239999999999998</v>
       </c>
       <c r="F41">
-        <v>22.776</v>
+        <v>23.36</v>
       </c>
       <c r="G41">
         <v>1.36</v>
@@ -4649,28 +4649,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M41">
-        <v>1.2367368</v>
+        <v>1.268448</v>
       </c>
       <c r="N41">
-        <v>7.656596533333334</v>
+        <v>7.624885333333334</v>
       </c>
       <c r="O41">
-        <v>2.067281064</v>
+        <v>2.05871904</v>
       </c>
       <c r="P41">
-        <v>5.589315469333334</v>
+        <v>5.566166293333334</v>
       </c>
       <c r="Q41">
-        <v>11.42931546933333</v>
+        <v>11.40616629333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0999845274068995</v>
+        <v>0.1007213610756719</v>
       </c>
       <c r="T41">
-        <v>0.9924086482774034</v>
+        <v>1.005904015686265</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.190966851906834</v>
+        <v>7.011192680609164</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07628841664540312</v>
+        <v>0.07612706157259752</v>
       </c>
       <c r="C42">
-        <v>38.01078431029279</v>
+        <v>37.74607157286943</v>
       </c>
       <c r="D42">
-        <v>60.01078431029279</v>
+        <v>60.33007157286944</v>
       </c>
       <c r="E42">
-        <v>-7.239999999999998</v>
+        <v>-6.655999999999999</v>
       </c>
       <c r="F42">
-        <v>23.36</v>
+        <v>23.944</v>
       </c>
       <c r="G42">
         <v>1.36</v>
@@ -4731,28 +4731,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M42">
-        <v>1.268448</v>
+        <v>1.3001592</v>
       </c>
       <c r="N42">
-        <v>7.624885333333334</v>
+        <v>7.593174133333334</v>
       </c>
       <c r="O42">
-        <v>2.05871904</v>
+        <v>2.050157016</v>
       </c>
       <c r="P42">
-        <v>5.566166293333334</v>
+        <v>5.543017117333333</v>
       </c>
       <c r="Q42">
-        <v>11.40616629333333</v>
+        <v>11.38301711733333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1007213610756719</v>
+        <v>0.101483172156945</v>
       </c>
       <c r="T42">
-        <v>1.005904015686265</v>
+        <v>1.019856853176783</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.011192680609164</v>
+        <v>6.840187981082111</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07612706157259752</v>
+        <v>0.07596570649979192</v>
       </c>
       <c r="C43">
-        <v>37.74607157286943</v>
+        <v>37.48477454324656</v>
       </c>
       <c r="D43">
-        <v>60.33007157286944</v>
+        <v>60.65277454324657</v>
       </c>
       <c r="E43">
-        <v>-6.655999999999999</v>
+        <v>-6.071999999999996</v>
       </c>
       <c r="F43">
-        <v>23.944</v>
+        <v>24.52800000000001</v>
       </c>
       <c r="G43">
         <v>1.36</v>
@@ -4813,28 +4813,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M43">
-        <v>1.3001592</v>
+        <v>1.3318704</v>
       </c>
       <c r="N43">
-        <v>7.593174133333334</v>
+        <v>7.561462933333334</v>
       </c>
       <c r="O43">
-        <v>2.050157016</v>
+        <v>2.041594992</v>
       </c>
       <c r="P43">
-        <v>5.543017117333333</v>
+        <v>5.519867941333334</v>
       </c>
       <c r="Q43">
-        <v>11.38301711733333</v>
+        <v>11.35986794133333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.101483172156945</v>
+        <v>0.1022712525858482</v>
       </c>
       <c r="T43">
-        <v>1.019856853176783</v>
+        <v>1.03429082299456</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.840187981082111</v>
+        <v>6.677326362484918</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07596570649979192</v>
+        <v>0.07580435142698634</v>
       </c>
       <c r="C44">
-        <v>37.48477454324656</v>
+        <v>37.22694832760918</v>
       </c>
       <c r="D44">
-        <v>60.65277454324657</v>
+        <v>60.97894832760918</v>
       </c>
       <c r="E44">
-        <v>-6.071999999999999</v>
+        <v>-5.488</v>
       </c>
       <c r="F44">
-        <v>24.528</v>
+        <v>25.112</v>
       </c>
       <c r="G44">
         <v>1.36</v>
@@ -4895,28 +4895,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M44">
-        <v>1.3318704</v>
+        <v>1.3635816</v>
       </c>
       <c r="N44">
-        <v>7.561462933333335</v>
+        <v>7.529751733333335</v>
       </c>
       <c r="O44">
-        <v>2.041594992000001</v>
+        <v>2.033032968000001</v>
       </c>
       <c r="P44">
-        <v>5.519867941333334</v>
+        <v>5.496718765333334</v>
       </c>
       <c r="Q44">
-        <v>11.35986794133333</v>
+        <v>11.33671876533333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1022712525858481</v>
+        <v>0.1030869849596251</v>
       </c>
       <c r="T44">
-        <v>1.03429082299456</v>
+        <v>1.049231247893663</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.677326362484919</v>
+        <v>6.522039702892247</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07580435142698634</v>
+        <v>0.07564299635418074</v>
       </c>
       <c r="C45">
-        <v>37.22694832760918</v>
+        <v>36.97264922393461</v>
       </c>
       <c r="D45">
-        <v>60.97894832760918</v>
+        <v>61.30864922393462</v>
       </c>
       <c r="E45">
-        <v>-5.488</v>
+        <v>-4.904</v>
       </c>
       <c r="F45">
-        <v>25.112</v>
+        <v>25.696</v>
       </c>
       <c r="G45">
         <v>1.36</v>
@@ -4977,28 +4977,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M45">
-        <v>1.3635816</v>
+        <v>1.3952928</v>
       </c>
       <c r="N45">
-        <v>7.529751733333335</v>
+        <v>7.498040533333334</v>
       </c>
       <c r="O45">
-        <v>2.033032968000001</v>
+        <v>2.024470944</v>
       </c>
       <c r="P45">
-        <v>5.496718765333334</v>
+        <v>5.473569589333334</v>
       </c>
       <c r="Q45">
-        <v>11.33671876533333</v>
+        <v>11.31356958933333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1030869849596251</v>
+        <v>0.1039318506324656</v>
       </c>
       <c r="T45">
-        <v>1.049231247893663</v>
+        <v>1.064705259396304</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.522039702892247</v>
+        <v>6.373811527826514</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07564299635418074</v>
+        <v>0.07548164128137516</v>
       </c>
       <c r="C46">
-        <v>36.97264922393461</v>
+        <v>36.7219347543863</v>
       </c>
       <c r="D46">
-        <v>61.30864922393462</v>
+        <v>61.64193475438631</v>
       </c>
       <c r="E46">
-        <v>-4.904</v>
+        <v>-4.319999999999997</v>
       </c>
       <c r="F46">
-        <v>25.696</v>
+        <v>26.28</v>
       </c>
       <c r="G46">
         <v>1.36</v>
@@ -5059,28 +5059,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M46">
-        <v>1.3952928</v>
+        <v>1.427004</v>
       </c>
       <c r="N46">
-        <v>7.498040533333334</v>
+        <v>7.466329333333334</v>
       </c>
       <c r="O46">
-        <v>2.024470944</v>
+        <v>2.01590892</v>
       </c>
       <c r="P46">
-        <v>5.473569589333334</v>
+        <v>5.450420413333334</v>
       </c>
       <c r="Q46">
-        <v>11.31356958933333</v>
+        <v>11.29042041333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1039318506324656</v>
+        <v>0.1048074386934094</v>
       </c>
       <c r="T46">
-        <v>1.064705259396304</v>
+        <v>1.080741962226315</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.373811527826514</v>
+        <v>6.232171271652589</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07548164128137516</v>
+        <v>0.07565608620856956</v>
       </c>
       <c r="C47">
-        <v>36.7219347543863</v>
+        <v>35.77776956912955</v>
       </c>
       <c r="D47">
-        <v>61.64193475438631</v>
+        <v>61.28176956912955</v>
       </c>
       <c r="E47">
-        <v>-4.319999999999997</v>
+        <v>-3.735999999999997</v>
       </c>
       <c r="F47">
-        <v>26.28</v>
+        <v>26.864</v>
       </c>
       <c r="G47">
         <v>1.36</v>
@@ -5141,45 +5141,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M47">
-        <v>1.427004</v>
+        <v>1.4855792</v>
       </c>
       <c r="N47">
-        <v>7.466329333333334</v>
+        <v>7.407754133333334</v>
       </c>
       <c r="O47">
-        <v>2.01590892</v>
+        <v>2.000093616</v>
       </c>
       <c r="P47">
-        <v>5.450420413333334</v>
+        <v>5.407660517333333</v>
       </c>
       <c r="Q47">
-        <v>11.29042041333333</v>
+        <v>11.24766051733333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1048074386934094</v>
+        <v>0.1057154559417955</v>
       </c>
       <c r="T47">
-        <v>1.080741962226315</v>
+        <v>1.097372617012993</v>
       </c>
       <c r="U47">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.232171271652589</v>
+        <v>5.986441741600403</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07565608620856956</v>
+        <v>0.07550203113576397</v>
       </c>
       <c r="C48">
-        <v>35.77776956912955</v>
+        <v>35.51161879060116</v>
       </c>
       <c r="D48">
-        <v>61.28176956912955</v>
+        <v>61.59961879060116</v>
       </c>
       <c r="E48">
-        <v>-3.735999999999997</v>
+        <v>-3.151999999999997</v>
       </c>
       <c r="F48">
-        <v>26.864</v>
+        <v>27.448</v>
       </c>
       <c r="G48">
         <v>1.36</v>
@@ -5223,28 +5223,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M48">
-        <v>1.4855792</v>
+        <v>1.5178744</v>
       </c>
       <c r="N48">
-        <v>7.407754133333334</v>
+        <v>7.375458933333334</v>
       </c>
       <c r="O48">
-        <v>2.000093616</v>
+        <v>1.991373912</v>
       </c>
       <c r="P48">
-        <v>5.407660517333333</v>
+        <v>5.384085021333334</v>
       </c>
       <c r="Q48">
-        <v>11.24766051733333</v>
+        <v>11.22408502133333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1057154559417955</v>
+        <v>0.1066577379920075</v>
       </c>
       <c r="T48">
-        <v>1.097372617012993</v>
+        <v>1.114630843678413</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.986441741600403</v>
+        <v>5.859070640715288</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07550203113576397</v>
+        <v>0.07534797606295837</v>
       </c>
       <c r="C49">
-        <v>35.51161879060116</v>
+        <v>35.24878237004102</v>
       </c>
       <c r="D49">
-        <v>61.59961879060116</v>
+        <v>61.92078237004102</v>
       </c>
       <c r="E49">
-        <v>-3.151999999999997</v>
+        <v>-2.567999999999998</v>
       </c>
       <c r="F49">
-        <v>27.448</v>
+        <v>28.032</v>
       </c>
       <c r="G49">
         <v>1.36</v>
@@ -5305,28 +5305,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M49">
-        <v>1.5178744</v>
+        <v>1.5501696</v>
       </c>
       <c r="N49">
-        <v>7.375458933333334</v>
+        <v>7.343163733333334</v>
       </c>
       <c r="O49">
-        <v>1.991373912</v>
+        <v>1.982654208</v>
       </c>
       <c r="P49">
-        <v>5.384085021333334</v>
+        <v>5.360509525333334</v>
       </c>
       <c r="Q49">
-        <v>11.22408502133333</v>
+        <v>11.20050952533333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1066577379920075</v>
+        <v>0.1076362616595353</v>
       </c>
       <c r="T49">
-        <v>1.114630843678413</v>
+        <v>1.132552848292504</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.859070640715288</v>
+        <v>5.737006669033719</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07534797606295837</v>
+        <v>0.07519392099015278</v>
       </c>
       <c r="C50">
-        <v>35.24878237004103</v>
+        <v>34.989312419618</v>
       </c>
       <c r="D50">
-        <v>61.92078237004102</v>
+        <v>62.245312419618</v>
       </c>
       <c r="E50">
-        <v>-2.568000000000001</v>
+        <v>-1.983999999999998</v>
       </c>
       <c r="F50">
-        <v>28.032</v>
+        <v>28.616</v>
       </c>
       <c r="G50">
         <v>1.36</v>
@@ -5387,28 +5387,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M50">
-        <v>1.5501696</v>
+        <v>1.5824648</v>
       </c>
       <c r="N50">
-        <v>7.343163733333334</v>
+        <v>7.310868533333334</v>
       </c>
       <c r="O50">
-        <v>1.982654208</v>
+        <v>1.973934504</v>
       </c>
       <c r="P50">
-        <v>5.360509525333334</v>
+        <v>5.336934029333333</v>
       </c>
       <c r="Q50">
-        <v>11.20050952533333</v>
+        <v>11.17693402933333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1076362616595353</v>
+        <v>0.1086531588042211</v>
       </c>
       <c r="T50">
-        <v>1.132552848292504</v>
+        <v>1.151177676616951</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.73700666903372</v>
+        <v>5.619924900277929</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07519392099015278</v>
+        <v>0.07503986591734718</v>
       </c>
       <c r="C51">
-        <v>34.989312419618</v>
+        <v>34.73326214974731</v>
       </c>
       <c r="D51">
-        <v>62.245312419618</v>
+        <v>62.57326214974731</v>
       </c>
       <c r="E51">
-        <v>-1.983999999999998</v>
+        <v>-1.399999999999999</v>
       </c>
       <c r="F51">
-        <v>28.616</v>
+        <v>29.2</v>
       </c>
       <c r="G51">
         <v>1.36</v>
@@ -5469,28 +5469,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M51">
-        <v>1.5824648</v>
+        <v>1.61476</v>
       </c>
       <c r="N51">
-        <v>7.310868533333334</v>
+        <v>7.278573333333334</v>
       </c>
       <c r="O51">
-        <v>1.973934504</v>
+        <v>1.9652148</v>
       </c>
       <c r="P51">
-        <v>5.336934029333333</v>
+        <v>5.313358533333334</v>
       </c>
       <c r="Q51">
-        <v>11.17693402933333</v>
+        <v>11.15335853333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1086531588042211</v>
+        <v>0.1097107318346944</v>
       </c>
       <c r="T51">
-        <v>1.151177676616951</v>
+        <v>1.170547498074376</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.619924900277929</v>
+        <v>5.50752640227237</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07503986591734718</v>
+        <v>0.0748858108445416</v>
       </c>
       <c r="C52">
-        <v>34.73326214974731</v>
+        <v>34.48068589817518</v>
       </c>
       <c r="D52">
-        <v>62.57326214974731</v>
+        <v>62.90468589817519</v>
       </c>
       <c r="E52">
-        <v>-1.399999999999999</v>
+        <v>-0.8159999999999989</v>
       </c>
       <c r="F52">
-        <v>29.2</v>
+        <v>29.784</v>
       </c>
       <c r="G52">
         <v>1.36</v>
@@ -5551,28 +5551,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M52">
-        <v>1.61476</v>
+        <v>1.6470552</v>
       </c>
       <c r="N52">
-        <v>7.278573333333334</v>
+        <v>7.246278133333334</v>
       </c>
       <c r="O52">
-        <v>1.9652148</v>
+        <v>1.956495096</v>
       </c>
       <c r="P52">
-        <v>5.313358533333334</v>
+        <v>5.289783037333334</v>
       </c>
       <c r="Q52">
-        <v>11.15335853333333</v>
+        <v>11.12978303733333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1097107318346944</v>
+        <v>0.1108114711113094</v>
       </c>
       <c r="T52">
-        <v>1.170547498074376</v>
+        <v>1.190707924489246</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.50752640227237</v>
+        <v>5.399535688502324</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0748858108445416</v>
+        <v>0.07473175577173601</v>
       </c>
       <c r="C53">
-        <v>34.48068589817518</v>
+        <v>34.23163915999289</v>
       </c>
       <c r="D53">
-        <v>62.90468589817519</v>
+        <v>63.2396391599929</v>
       </c>
       <c r="E53">
-        <v>-0.8159999999999989</v>
+        <v>-0.2319999999999958</v>
       </c>
       <c r="F53">
-        <v>29.784</v>
+        <v>30.36800000000001</v>
       </c>
       <c r="G53">
         <v>1.36</v>
@@ -5633,28 +5633,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M53">
-        <v>1.6470552</v>
+        <v>1.6793504</v>
       </c>
       <c r="N53">
-        <v>7.246278133333334</v>
+        <v>7.213982933333334</v>
       </c>
       <c r="O53">
-        <v>1.956495096</v>
+        <v>1.947775392</v>
       </c>
       <c r="P53">
-        <v>5.289783037333334</v>
+        <v>5.266207541333333</v>
       </c>
       <c r="Q53">
-        <v>11.12978303733333</v>
+        <v>11.10620754133333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1108114711113094</v>
+        <v>0.11195807452445</v>
       </c>
       <c r="T53">
-        <v>1.190707924489246</v>
+        <v>1.211708368671403</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.399535688502324</v>
+        <v>5.295698463723433</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07473175577173601</v>
+        <v>0.07457770069893041</v>
       </c>
       <c r="C54">
-        <v>34.23163915999289</v>
+        <v>33.98617861861457</v>
       </c>
       <c r="D54">
-        <v>63.2396391599929</v>
+        <v>63.57817861861457</v>
       </c>
       <c r="E54">
-        <v>-0.2319999999999958</v>
+        <v>0.3520000000000039</v>
       </c>
       <c r="F54">
-        <v>30.36800000000001</v>
+        <v>30.95200000000001</v>
       </c>
       <c r="G54">
         <v>1.36</v>
@@ -5715,28 +5715,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M54">
-        <v>1.6793504</v>
+        <v>1.7116456</v>
       </c>
       <c r="N54">
-        <v>7.213982933333334</v>
+        <v>7.181687733333334</v>
       </c>
       <c r="O54">
-        <v>1.947775392</v>
+        <v>1.939055688</v>
       </c>
       <c r="P54">
-        <v>5.266207541333333</v>
+        <v>5.242632045333334</v>
       </c>
       <c r="Q54">
-        <v>11.10620754133333</v>
+        <v>11.08263204533333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.11195807452445</v>
+        <v>0.1131534695721924</v>
       </c>
       <c r="T54">
-        <v>1.211708368671403</v>
+        <v>1.233602448776205</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.295698463723433</v>
+        <v>5.195779624785255</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07457770069893041</v>
+        <v>0.07442364562612482</v>
       </c>
       <c r="C55">
-        <v>33.98617861861457</v>
+        <v>33.74436217775556</v>
       </c>
       <c r="D55">
-        <v>63.57817861861457</v>
+        <v>63.92036217775556</v>
       </c>
       <c r="E55">
-        <v>0.3520000000000039</v>
+        <v>0.9360000000000035</v>
       </c>
       <c r="F55">
-        <v>30.95200000000001</v>
+        <v>31.536</v>
       </c>
       <c r="G55">
         <v>1.36</v>
@@ -5797,28 +5797,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M55">
-        <v>1.7116456</v>
+        <v>1.7439408</v>
       </c>
       <c r="N55">
-        <v>7.181687733333334</v>
+        <v>7.149392533333334</v>
       </c>
       <c r="O55">
-        <v>1.939055688</v>
+        <v>1.930335984</v>
       </c>
       <c r="P55">
-        <v>5.242632045333334</v>
+        <v>5.219056549333334</v>
       </c>
       <c r="Q55">
-        <v>11.08263204533333</v>
+        <v>11.05905654933333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1131534695721924</v>
+        <v>0.1144008383176627</v>
       </c>
       <c r="T55">
-        <v>1.233602448776205</v>
+        <v>1.256448445407303</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.195779624785255</v>
+        <v>5.099561483585528</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07442364562612482</v>
+        <v>0.07426959055331922</v>
       </c>
       <c r="C56">
-        <v>33.74436217775556</v>
+        <v>33.50624899444902</v>
       </c>
       <c r="D56">
-        <v>63.92036217775556</v>
+        <v>64.26624899444903</v>
       </c>
       <c r="E56">
-        <v>0.9360000000000035</v>
+        <v>1.520000000000003</v>
       </c>
       <c r="F56">
-        <v>31.536</v>
+        <v>32.12</v>
       </c>
       <c r="G56">
         <v>1.36</v>
@@ -5879,28 +5879,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M56">
-        <v>1.7439408</v>
+        <v>1.776236</v>
       </c>
       <c r="N56">
-        <v>7.149392533333334</v>
+        <v>7.117097333333334</v>
       </c>
       <c r="O56">
-        <v>1.930335984</v>
+        <v>1.92161628</v>
       </c>
       <c r="P56">
-        <v>5.219056549333334</v>
+        <v>5.195481053333333</v>
       </c>
       <c r="Q56">
-        <v>11.05905654933333</v>
+        <v>11.03548105333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1144008383176627</v>
+        <v>0.1157036456740427</v>
       </c>
       <c r="T56">
-        <v>1.256448445407303</v>
+        <v>1.28030981966645</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.099561483585528</v>
+        <v>5.006842183883973</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07426959055331922</v>
+        <v>0.07411553548051364</v>
       </c>
       <c r="C57">
-        <v>33.50624899444902</v>
+        <v>33.27189951314024</v>
       </c>
       <c r="D57">
-        <v>64.26624899444903</v>
+        <v>64.61589951314025</v>
       </c>
       <c r="E57">
-        <v>1.520000000000003</v>
+        <v>2.104000000000006</v>
       </c>
       <c r="F57">
-        <v>32.12</v>
+        <v>32.70400000000001</v>
       </c>
       <c r="G57">
         <v>1.36</v>
@@ -5961,28 +5961,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M57">
-        <v>1.776236</v>
+        <v>1.8085312</v>
       </c>
       <c r="N57">
-        <v>7.117097333333334</v>
+        <v>7.084802133333334</v>
       </c>
       <c r="O57">
-        <v>1.92161628</v>
+        <v>1.912896576</v>
       </c>
       <c r="P57">
-        <v>5.195481053333333</v>
+        <v>5.171905557333334</v>
       </c>
       <c r="Q57">
-        <v>11.03548105333333</v>
+        <v>11.01190555733333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1157036456740427</v>
+        <v>0.1170656715466219</v>
       </c>
       <c r="T57">
-        <v>1.28030981966645</v>
+        <v>1.305255801846466</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.006842183883973</v>
+        <v>4.917434287743188</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07411553548051364</v>
+        <v>0.07396148040770803</v>
       </c>
       <c r="C58">
-        <v>33.27189951314024</v>
+        <v>33.04137550090018</v>
       </c>
       <c r="D58">
-        <v>64.61589951314025</v>
+        <v>64.96937550090018</v>
       </c>
       <c r="E58">
-        <v>2.104000000000006</v>
+        <v>2.688000000000002</v>
       </c>
       <c r="F58">
-        <v>32.70400000000001</v>
+        <v>33.288</v>
       </c>
       <c r="G58">
         <v>1.36</v>
@@ -6043,28 +6043,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M58">
-        <v>1.8085312</v>
+        <v>1.8408264</v>
       </c>
       <c r="N58">
-        <v>7.084802133333334</v>
+        <v>7.052506933333334</v>
       </c>
       <c r="O58">
-        <v>1.912896576</v>
+        <v>1.904176872</v>
       </c>
       <c r="P58">
-        <v>5.171905557333334</v>
+        <v>5.148330061333334</v>
       </c>
       <c r="Q58">
-        <v>11.01190555733333</v>
+        <v>10.98833006133333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1170656715466219</v>
+        <v>0.1184910474597861</v>
       </c>
       <c r="T58">
-        <v>1.305255801846466</v>
+        <v>1.331362062267414</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.917434287743188</v>
+        <v>4.831163510765237</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07396148040770803</v>
+        <v>0.07380742533490246</v>
       </c>
       <c r="C59">
-        <v>33.04137550090018</v>
+        <v>32.81474008380065</v>
       </c>
       <c r="D59">
-        <v>64.96937550090018</v>
+        <v>65.32674008380066</v>
       </c>
       <c r="E59">
-        <v>2.688000000000002</v>
+        <v>3.272000000000006</v>
       </c>
       <c r="F59">
-        <v>33.288</v>
+        <v>33.87200000000001</v>
       </c>
       <c r="G59">
         <v>1.36</v>
@@ -6125,28 +6125,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M59">
-        <v>1.8408264</v>
+        <v>1.8731216</v>
       </c>
       <c r="N59">
-        <v>7.052506933333334</v>
+        <v>7.020211733333334</v>
       </c>
       <c r="O59">
-        <v>1.904176872</v>
+        <v>1.895457168</v>
       </c>
       <c r="P59">
-        <v>5.148330061333334</v>
+        <v>5.124754565333334</v>
       </c>
       <c r="Q59">
-        <v>10.98833006133333</v>
+        <v>10.96475456533333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1184910474597861</v>
+        <v>0.1199842984164344</v>
       </c>
       <c r="T59">
-        <v>1.331362062267414</v>
+        <v>1.358711477946502</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.831163510765237</v>
+        <v>4.747867588165837</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07380742533490245</v>
+        <v>0.07365337026209685</v>
       </c>
       <c r="C60">
-        <v>32.8147400838007</v>
+        <v>32.59205778449765</v>
       </c>
       <c r="D60">
-        <v>65.3267400838007</v>
+        <v>65.68805778449766</v>
       </c>
       <c r="E60">
-        <v>3.271999999999998</v>
+        <v>3.856000000000002</v>
       </c>
       <c r="F60">
-        <v>33.872</v>
+        <v>34.456</v>
       </c>
       <c r="G60">
         <v>1.36</v>
@@ -6207,28 +6207,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M60">
-        <v>1.8731216</v>
+        <v>1.9054168</v>
       </c>
       <c r="N60">
-        <v>7.020211733333334</v>
+        <v>6.987916533333334</v>
       </c>
       <c r="O60">
-        <v>1.895457168</v>
+        <v>1.886737464</v>
       </c>
       <c r="P60">
-        <v>5.124754565333334</v>
+        <v>5.101179069333334</v>
       </c>
       <c r="Q60">
-        <v>10.96475456533333</v>
+        <v>10.94117906933333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1199842984164344</v>
+        <v>0.1215503908831631</v>
       </c>
       <c r="T60">
-        <v>1.358711477946502</v>
+        <v>1.387395011463594</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.747867588165837</v>
+        <v>4.667395256163026</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07365337026209685</v>
+        <v>0.07349931518929126</v>
       </c>
       <c r="C61">
-        <v>32.59205778449765</v>
+        <v>32.37339456106753</v>
       </c>
       <c r="D61">
-        <v>65.68805778449766</v>
+        <v>66.05339456106753</v>
       </c>
       <c r="E61">
-        <v>3.856000000000002</v>
+        <v>4.439999999999998</v>
       </c>
       <c r="F61">
-        <v>34.456</v>
+        <v>35.04</v>
       </c>
       <c r="G61">
         <v>1.36</v>
@@ -6289,28 +6289,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M61">
-        <v>1.9054168</v>
+        <v>1.937712</v>
       </c>
       <c r="N61">
-        <v>6.987916533333334</v>
+        <v>6.955621333333334</v>
       </c>
       <c r="O61">
-        <v>1.886737464</v>
+        <v>1.87801776</v>
       </c>
       <c r="P61">
-        <v>5.101179069333334</v>
+        <v>5.077603573333334</v>
       </c>
       <c r="Q61">
-        <v>10.94117906933333</v>
+        <v>10.91760357333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1215503908831631</v>
+        <v>0.1231947879732281</v>
       </c>
       <c r="T61">
-        <v>1.387395011463594</v>
+        <v>1.417512721656541</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.667395256163026</v>
+        <v>4.589605335226976</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07349931518929126</v>
+        <v>0.07334526011648568</v>
       </c>
       <c r="C62">
-        <v>32.37339456106753</v>
+        <v>32.15881784714757</v>
       </c>
       <c r="D62">
-        <v>66.05339456106753</v>
+        <v>66.42281784714757</v>
       </c>
       <c r="E62">
-        <v>4.439999999999998</v>
+        <v>5.024000000000001</v>
       </c>
       <c r="F62">
-        <v>35.04</v>
+        <v>35.624</v>
       </c>
       <c r="G62">
         <v>1.36</v>
@@ -6371,28 +6371,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M62">
-        <v>1.937712</v>
+        <v>1.9700072</v>
       </c>
       <c r="N62">
-        <v>6.955621333333334</v>
+        <v>6.923326133333334</v>
       </c>
       <c r="O62">
-        <v>1.87801776</v>
+        <v>1.869298056</v>
       </c>
       <c r="P62">
-        <v>5.077603573333334</v>
+        <v>5.054028077333333</v>
       </c>
       <c r="Q62">
-        <v>10.91760357333333</v>
+        <v>10.89402807733333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1231947879732281</v>
+        <v>0.124923513119194</v>
       </c>
       <c r="T62">
-        <v>1.417512721656541</v>
+        <v>1.449174929808101</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.589605335226976</v>
+        <v>4.514365903501943</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07334526011648568</v>
+        <v>0.07432270504368008</v>
       </c>
       <c r="C63">
-        <v>32.15881784714757</v>
+        <v>29.2985734918094</v>
       </c>
       <c r="D63">
-        <v>66.42281784714757</v>
+        <v>64.14657349180941</v>
       </c>
       <c r="E63">
-        <v>5.024000000000001</v>
+        <v>5.608000000000004</v>
       </c>
       <c r="F63">
-        <v>35.624</v>
+        <v>36.20800000000001</v>
       </c>
       <c r="G63">
         <v>1.36</v>
@@ -6453,45 +6453,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M63">
-        <v>1.9700072</v>
+        <v>2.092822400000001</v>
       </c>
       <c r="N63">
-        <v>6.923326133333334</v>
+        <v>6.800510933333333</v>
       </c>
       <c r="O63">
-        <v>1.869298056</v>
+        <v>1.836137952</v>
       </c>
       <c r="P63">
-        <v>5.054028077333333</v>
+        <v>4.964372981333334</v>
       </c>
       <c r="Q63">
-        <v>10.89402807733333</v>
+        <v>10.80437298133333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.124923513119194</v>
+        <v>0.1267432237991581</v>
       </c>
       <c r="T63">
-        <v>1.449174929808101</v>
+        <v>1.482503569967638</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.514365903501943</v>
+        <v>4.249444832649599</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07432270504368008</v>
+        <v>0.07418689997087448</v>
       </c>
       <c r="C64">
-        <v>29.2985734918094</v>
+        <v>29.02145554276329</v>
       </c>
       <c r="D64">
-        <v>64.14657349180941</v>
+        <v>64.45345554276329</v>
       </c>
       <c r="E64">
-        <v>5.608000000000004</v>
+        <v>6.192</v>
       </c>
       <c r="F64">
-        <v>36.20800000000001</v>
+        <v>36.792</v>
       </c>
       <c r="G64">
         <v>1.36</v>
@@ -6535,28 +6535,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M64">
-        <v>2.092822400000001</v>
+        <v>2.1265776</v>
       </c>
       <c r="N64">
-        <v>6.800510933333333</v>
+        <v>6.766755733333334</v>
       </c>
       <c r="O64">
-        <v>1.836137952</v>
+        <v>1.827024048</v>
       </c>
       <c r="P64">
-        <v>4.964372981333334</v>
+        <v>4.939731685333334</v>
       </c>
       <c r="Q64">
-        <v>10.80437298133333</v>
+        <v>10.77973168533333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1267432237991581</v>
+        <v>0.1286612972185797</v>
       </c>
       <c r="T64">
-        <v>1.482503569967638</v>
+        <v>1.517633758243906</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.249444832649599</v>
+        <v>4.181993327369447</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07418689997087448</v>
+        <v>0.07405109489806889</v>
       </c>
       <c r="C65">
-        <v>29.02145554276329</v>
+        <v>28.74728800250115</v>
       </c>
       <c r="D65">
-        <v>64.45345554276329</v>
+        <v>64.76328800250116</v>
       </c>
       <c r="E65">
-        <v>6.192</v>
+        <v>6.776000000000003</v>
       </c>
       <c r="F65">
-        <v>36.792</v>
+        <v>37.376</v>
       </c>
       <c r="G65">
         <v>1.36</v>
@@ -6617,28 +6617,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M65">
-        <v>2.1265776</v>
+        <v>2.1603328</v>
       </c>
       <c r="N65">
-        <v>6.766755733333334</v>
+        <v>6.733000533333334</v>
       </c>
       <c r="O65">
-        <v>1.827024048</v>
+        <v>1.817910144</v>
       </c>
       <c r="P65">
-        <v>4.939731685333334</v>
+        <v>4.915090389333333</v>
       </c>
       <c r="Q65">
-        <v>10.77973168533333</v>
+        <v>10.75509038933333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1286612972185797</v>
+        <v>0.1306859302724136</v>
       </c>
       <c r="T65">
-        <v>1.517633758243906</v>
+        <v>1.554715623646634</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.181993327369447</v>
+        <v>4.116649681629299</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07405109489806889</v>
+        <v>0.0739152898252633</v>
       </c>
       <c r="C66">
-        <v>28.74728800250115</v>
+        <v>28.47611362503507</v>
       </c>
       <c r="D66">
-        <v>64.76328800250116</v>
+        <v>65.07611362503508</v>
       </c>
       <c r="E66">
-        <v>6.776000000000003</v>
+        <v>7.360000000000007</v>
       </c>
       <c r="F66">
-        <v>37.376</v>
+        <v>37.96000000000001</v>
       </c>
       <c r="G66">
         <v>1.36</v>
@@ -6699,28 +6699,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M66">
-        <v>2.1603328</v>
+        <v>2.194088000000001</v>
       </c>
       <c r="N66">
-        <v>6.733000533333334</v>
+        <v>6.699245333333334</v>
       </c>
       <c r="O66">
-        <v>1.817910144</v>
+        <v>1.80879624</v>
       </c>
       <c r="P66">
-        <v>4.915090389333333</v>
+        <v>4.890449093333333</v>
       </c>
       <c r="Q66">
-        <v>10.75509038933333</v>
+        <v>10.73044909333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1306859302724136</v>
+        <v>0.1328262566436094</v>
       </c>
       <c r="T66">
-        <v>1.554715623646634</v>
+        <v>1.59391645278666</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.116649681629299</v>
+        <v>4.053316609604233</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0739152898252633</v>
+        <v>0.0754657847524577</v>
       </c>
       <c r="C67">
-        <v>28.47611362503507</v>
+        <v>24.49088271545044</v>
       </c>
       <c r="D67">
-        <v>65.07611362503508</v>
+        <v>61.67488271545044</v>
       </c>
       <c r="E67">
-        <v>7.360000000000007</v>
+        <v>7.944000000000003</v>
       </c>
       <c r="F67">
-        <v>37.96000000000001</v>
+        <v>38.544</v>
       </c>
       <c r="G67">
         <v>1.36</v>
@@ -6781,45 +6781,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M67">
-        <v>2.194088000000001</v>
+        <v>2.3627472</v>
       </c>
       <c r="N67">
-        <v>6.699245333333334</v>
+        <v>6.530586133333334</v>
       </c>
       <c r="O67">
-        <v>1.80879624</v>
+        <v>1.763258256</v>
       </c>
       <c r="P67">
-        <v>4.890449093333333</v>
+        <v>4.767327877333334</v>
       </c>
       <c r="Q67">
-        <v>10.73044909333333</v>
+        <v>10.60732787733333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1328262566436094</v>
+        <v>0.1350924845660521</v>
       </c>
       <c r="T67">
-        <v>1.59391645278666</v>
+        <v>1.63542321305257</v>
       </c>
       <c r="U67">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.053316609604233</v>
+        <v>3.763980053953014</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0754657847524577</v>
+        <v>0.07535552967965212</v>
       </c>
       <c r="C68">
-        <v>24.49088271545044</v>
+        <v>24.13695704528894</v>
       </c>
       <c r="D68">
-        <v>61.67488271545044</v>
+        <v>61.90495704528895</v>
       </c>
       <c r="E68">
-        <v>7.944000000000003</v>
+        <v>8.528000000000006</v>
       </c>
       <c r="F68">
-        <v>38.544</v>
+        <v>39.12800000000001</v>
       </c>
       <c r="G68">
         <v>1.36</v>
@@ -6863,28 +6863,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M68">
-        <v>2.3627472</v>
+        <v>2.3985464</v>
       </c>
       <c r="N68">
-        <v>6.530586133333334</v>
+        <v>6.494786933333334</v>
       </c>
       <c r="O68">
-        <v>1.763258256</v>
+        <v>1.753592472</v>
       </c>
       <c r="P68">
-        <v>4.767327877333334</v>
+        <v>4.741194461333333</v>
       </c>
       <c r="Q68">
-        <v>10.60732787733333</v>
+        <v>10.58119446133333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1350924845660521</v>
+        <v>0.1374960596353094</v>
       </c>
       <c r="T68">
-        <v>1.63542321305257</v>
+        <v>1.679445534546718</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.763980053953014</v>
+        <v>3.707801247177596</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07535552967965212</v>
+        <v>0.07524527460684652</v>
       </c>
       <c r="C69">
-        <v>24.13695704528894</v>
+        <v>23.7847543586843</v>
       </c>
       <c r="D69">
-        <v>61.90495704528895</v>
+        <v>62.13675435868431</v>
       </c>
       <c r="E69">
-        <v>8.528000000000006</v>
+        <v>9.112000000000002</v>
       </c>
       <c r="F69">
-        <v>39.12800000000001</v>
+        <v>39.712</v>
       </c>
       <c r="G69">
         <v>1.36</v>
@@ -6945,28 +6945,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M69">
-        <v>2.3985464</v>
+        <v>2.4343456</v>
       </c>
       <c r="N69">
-        <v>6.494786933333334</v>
+        <v>6.458987733333334</v>
       </c>
       <c r="O69">
-        <v>1.753592472</v>
+        <v>1.743926688</v>
       </c>
       <c r="P69">
-        <v>4.741194461333333</v>
+        <v>4.715061045333334</v>
       </c>
       <c r="Q69">
-        <v>10.58119446133333</v>
+        <v>10.55506104533333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1374960596353094</v>
+        <v>0.1400498581463954</v>
       </c>
       <c r="T69">
-        <v>1.679445534546718</v>
+        <v>1.726219251134249</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.707801247177596</v>
+        <v>3.653274758248514</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07524527460684652</v>
+        <v>0.07513501953404093</v>
       </c>
       <c r="C70">
-        <v>23.7847543586843</v>
+        <v>23.43429408303218</v>
       </c>
       <c r="D70">
-        <v>62.13675435868431</v>
+        <v>62.37029408303219</v>
       </c>
       <c r="E70">
-        <v>9.112000000000002</v>
+        <v>9.696000000000005</v>
       </c>
       <c r="F70">
-        <v>39.712</v>
+        <v>40.29600000000001</v>
       </c>
       <c r="G70">
         <v>1.36</v>
@@ -7027,28 +7027,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M70">
-        <v>2.4343456</v>
+        <v>2.4701448</v>
       </c>
       <c r="N70">
-        <v>6.458987733333334</v>
+        <v>6.423188533333335</v>
       </c>
       <c r="O70">
-        <v>1.743926688</v>
+        <v>1.734260904</v>
       </c>
       <c r="P70">
-        <v>4.715061045333334</v>
+        <v>4.688927629333334</v>
       </c>
       <c r="Q70">
-        <v>10.55506104533333</v>
+        <v>10.52892762933334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1400498581463954</v>
+        <v>0.142768417851745</v>
       </c>
       <c r="T70">
-        <v>1.726219251134249</v>
+        <v>1.77601062685646</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.653274758248514</v>
+        <v>3.600328747259405</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07513501953404093</v>
+        <v>0.07502476446123534</v>
       </c>
       <c r="C71">
-        <v>23.43429408303218</v>
+        <v>23.08559593890008</v>
       </c>
       <c r="D71">
-        <v>62.37029408303219</v>
+        <v>62.60559593890009</v>
       </c>
       <c r="E71">
-        <v>9.696000000000005</v>
+        <v>10.28000000000001</v>
       </c>
       <c r="F71">
-        <v>40.29600000000001</v>
+        <v>40.88000000000001</v>
       </c>
       <c r="G71">
         <v>1.36</v>
@@ -7109,28 +7109,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M71">
-        <v>2.4701448</v>
+        <v>2.505944</v>
       </c>
       <c r="N71">
-        <v>6.423188533333335</v>
+        <v>6.387389333333334</v>
       </c>
       <c r="O71">
-        <v>1.734260904</v>
+        <v>1.72459512</v>
       </c>
       <c r="P71">
-        <v>4.688927629333334</v>
+        <v>4.662794213333334</v>
       </c>
       <c r="Q71">
-        <v>10.52892762933334</v>
+        <v>10.50279421333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.142768417851745</v>
+        <v>0.1456682148707845</v>
       </c>
       <c r="T71">
-        <v>1.77601062685646</v>
+        <v>1.829121427626818</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.600328747259405</v>
+        <v>3.548895479441413</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07502476446123534</v>
+        <v>0.07636574938842974</v>
       </c>
       <c r="C72">
-        <v>23.08559593890008</v>
+        <v>19.75495428306463</v>
       </c>
       <c r="D72">
-        <v>62.60559593890009</v>
+        <v>59.85895428306463</v>
       </c>
       <c r="E72">
-        <v>10.28000000000001</v>
+        <v>10.864</v>
       </c>
       <c r="F72">
-        <v>40.88000000000001</v>
+        <v>41.46400000000001</v>
       </c>
       <c r="G72">
         <v>1.36</v>
@@ -7191,45 +7191,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M72">
-        <v>2.505944</v>
+        <v>2.657842400000001</v>
       </c>
       <c r="N72">
-        <v>6.387389333333334</v>
+        <v>6.235490933333334</v>
       </c>
       <c r="O72">
-        <v>1.72459512</v>
+        <v>1.683582552</v>
       </c>
       <c r="P72">
-        <v>4.662794213333334</v>
+        <v>4.551908381333334</v>
       </c>
       <c r="Q72">
-        <v>10.50279421333333</v>
+        <v>10.39190838133333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1456682148707845</v>
+        <v>0.1487679978911371</v>
       </c>
       <c r="T72">
-        <v>1.829121427626818</v>
+        <v>1.885895042243408</v>
       </c>
       <c r="U72">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.548895479441413</v>
+        <v>3.346072488471601</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07636574938842974</v>
+        <v>0.07627593431562416</v>
       </c>
       <c r="C73">
-        <v>19.75495428306463</v>
+        <v>19.34736352063945</v>
       </c>
       <c r="D73">
-        <v>59.85895428306463</v>
+        <v>60.03536352063946</v>
       </c>
       <c r="E73">
-        <v>10.864</v>
+        <v>11.448</v>
       </c>
       <c r="F73">
-        <v>41.464</v>
+        <v>42.048</v>
       </c>
       <c r="G73">
         <v>1.36</v>
@@ -7273,28 +7273,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M73">
-        <v>2.6578424</v>
+        <v>2.6952768</v>
       </c>
       <c r="N73">
-        <v>6.235490933333335</v>
+        <v>6.198056533333334</v>
       </c>
       <c r="O73">
-        <v>1.683582552000001</v>
+        <v>1.673475264</v>
       </c>
       <c r="P73">
-        <v>4.551908381333334</v>
+        <v>4.524581269333334</v>
       </c>
       <c r="Q73">
-        <v>10.39190838133333</v>
+        <v>10.36458126933333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.148767997891137</v>
+        <v>0.152089193984372</v>
       </c>
       <c r="T73">
-        <v>1.885895042243408</v>
+        <v>1.946723915046897</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.346072488471602</v>
+        <v>3.299599259465051</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07627593431562416</v>
+        <v>0.07618611924281855</v>
       </c>
       <c r="C74">
-        <v>19.34736352063945</v>
+        <v>18.94081561652668</v>
       </c>
       <c r="D74">
-        <v>60.03536352063946</v>
+        <v>60.21281561652668</v>
       </c>
       <c r="E74">
-        <v>11.448</v>
+        <v>12.032</v>
       </c>
       <c r="F74">
-        <v>42.048</v>
+        <v>42.63200000000001</v>
       </c>
       <c r="G74">
         <v>1.36</v>
@@ -7355,28 +7355,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M74">
-        <v>2.6952768</v>
+        <v>2.732711200000001</v>
       </c>
       <c r="N74">
-        <v>6.198056533333334</v>
+        <v>6.160622133333334</v>
       </c>
       <c r="O74">
-        <v>1.673475264</v>
+        <v>1.663367976</v>
       </c>
       <c r="P74">
-        <v>4.524581269333334</v>
+        <v>4.497254157333334</v>
       </c>
       <c r="Q74">
-        <v>10.36458126933333</v>
+        <v>10.33725415733333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.152089193984372</v>
+        <v>0.1556564046030317</v>
       </c>
       <c r="T74">
-        <v>1.946723915046897</v>
+        <v>2.012058630280274</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.299599259465051</v>
+        <v>3.254399269609365</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07618611924281855</v>
+        <v>0.07609630417001298</v>
       </c>
       <c r="C75">
-        <v>18.94081561652668</v>
+        <v>18.53531984555999</v>
       </c>
       <c r="D75">
-        <v>60.21281561652668</v>
+        <v>60.39131984555999</v>
       </c>
       <c r="E75">
-        <v>12.032</v>
+        <v>12.616</v>
       </c>
       <c r="F75">
-        <v>42.63200000000001</v>
+        <v>43.216</v>
       </c>
       <c r="G75">
         <v>1.36</v>
@@ -7437,28 +7437,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M75">
-        <v>2.732711200000001</v>
+        <v>2.7701456</v>
       </c>
       <c r="N75">
-        <v>6.160622133333334</v>
+        <v>6.123187733333334</v>
       </c>
       <c r="O75">
-        <v>1.663367976</v>
+        <v>1.653260688</v>
       </c>
       <c r="P75">
-        <v>4.497254157333334</v>
+        <v>4.469927045333334</v>
       </c>
       <c r="Q75">
-        <v>10.33725415733333</v>
+        <v>10.30992704533333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1556564046030317</v>
+        <v>0.1594980160385114</v>
       </c>
       <c r="T75">
-        <v>2.012058630280274</v>
+        <v>2.082419092839296</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.254399269609365</v>
+        <v>3.210420901101131</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07609630417001298</v>
+        <v>0.07600648909720738</v>
       </c>
       <c r="C76">
-        <v>18.53531984555999</v>
+        <v>18.13088559288337</v>
       </c>
       <c r="D76">
-        <v>60.39131984555999</v>
+        <v>60.57088559288337</v>
       </c>
       <c r="E76">
-        <v>12.616</v>
+        <v>13.2</v>
       </c>
       <c r="F76">
-        <v>43.216</v>
+        <v>43.8</v>
       </c>
       <c r="G76">
         <v>1.36</v>
@@ -7519,28 +7519,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M76">
-        <v>2.7701456</v>
+        <v>2.807580000000001</v>
       </c>
       <c r="N76">
-        <v>6.123187733333334</v>
+        <v>6.085753333333334</v>
       </c>
       <c r="O76">
-        <v>1.653260688</v>
+        <v>1.6431534</v>
       </c>
       <c r="P76">
-        <v>4.469927045333334</v>
+        <v>4.442599933333334</v>
       </c>
       <c r="Q76">
-        <v>10.30992704533333</v>
+        <v>10.28259993333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1594980160385114</v>
+        <v>0.1636469563888295</v>
       </c>
       <c r="T76">
-        <v>2.082419092839296</v>
+        <v>2.158408392403039</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.210420901101131</v>
+        <v>3.167615289086449</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07600648909720738</v>
+        <v>0.07591667402440179</v>
       </c>
       <c r="C77">
-        <v>18.13088559288337</v>
+        <v>17.72752235559548</v>
       </c>
       <c r="D77">
-        <v>60.57088559288337</v>
+        <v>60.75152235559548</v>
       </c>
       <c r="E77">
-        <v>13.2</v>
+        <v>13.78400000000001</v>
       </c>
       <c r="F77">
-        <v>43.8</v>
+        <v>44.38400000000001</v>
       </c>
       <c r="G77">
         <v>1.36</v>
@@ -7601,28 +7601,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M77">
-        <v>2.807580000000001</v>
+        <v>2.845014400000001</v>
       </c>
       <c r="N77">
-        <v>6.085753333333334</v>
+        <v>6.048318933333334</v>
       </c>
       <c r="O77">
-        <v>1.6431534</v>
+        <v>1.633046112</v>
       </c>
       <c r="P77">
-        <v>4.442599933333334</v>
+        <v>4.415272821333334</v>
       </c>
       <c r="Q77">
-        <v>10.28259993333333</v>
+        <v>10.25527282133333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1636469563888295</v>
+        <v>0.1681416417683408</v>
       </c>
       <c r="T77">
-        <v>2.158408392403039</v>
+        <v>2.240730133597095</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.167615289086449</v>
+        <v>3.125936140545838</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07591667402440179</v>
+        <v>0.07582685895159619</v>
       </c>
       <c r="C78">
-        <v>17.72752235559548</v>
+        <v>17.32523974442441</v>
       </c>
       <c r="D78">
-        <v>60.75152235559548</v>
+        <v>60.93323974442441</v>
       </c>
       <c r="E78">
-        <v>13.78400000000001</v>
+        <v>14.368</v>
       </c>
       <c r="F78">
-        <v>44.38400000000001</v>
+        <v>44.968</v>
       </c>
       <c r="G78">
         <v>1.36</v>
@@ -7683,28 +7683,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M78">
-        <v>2.845014400000001</v>
+        <v>2.882448800000001</v>
       </c>
       <c r="N78">
-        <v>6.048318933333334</v>
+        <v>6.010884533333334</v>
       </c>
       <c r="O78">
-        <v>1.633046112</v>
+        <v>1.622938824</v>
       </c>
       <c r="P78">
-        <v>4.415272821333334</v>
+        <v>4.387945709333334</v>
       </c>
       <c r="Q78">
-        <v>10.25527282133333</v>
+        <v>10.22794570933333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1681416417683408</v>
+        <v>0.1730271693547661</v>
       </c>
       <c r="T78">
-        <v>2.240730133597095</v>
+        <v>2.330210287068894</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.125936140545838</v>
+        <v>3.085339567291996</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07582685895159619</v>
+        <v>0.0757370438787906</v>
       </c>
       <c r="C79">
-        <v>17.32523974442441</v>
+        <v>16.92404748543196</v>
       </c>
       <c r="D79">
-        <v>60.93323974442441</v>
+        <v>61.11604748543197</v>
       </c>
       <c r="E79">
-        <v>14.368</v>
+        <v>14.95200000000001</v>
       </c>
       <c r="F79">
-        <v>44.968</v>
+        <v>45.55200000000001</v>
       </c>
       <c r="G79">
         <v>1.36</v>
@@ -7765,28 +7765,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M79">
-        <v>2.882448800000001</v>
+        <v>2.919883200000001</v>
       </c>
       <c r="N79">
-        <v>6.010884533333334</v>
+        <v>5.973450133333333</v>
       </c>
       <c r="O79">
-        <v>1.622938824</v>
+        <v>1.612831536</v>
       </c>
       <c r="P79">
-        <v>4.387945709333334</v>
+        <v>4.360618597333334</v>
       </c>
       <c r="Q79">
-        <v>10.22794570933333</v>
+        <v>10.20061859733333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1730271693547661</v>
+        <v>0.1783568358126845</v>
       </c>
       <c r="T79">
-        <v>2.330210287068894</v>
+        <v>2.42782499994722</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.085339567291996</v>
+        <v>3.045783931813893</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0757370438787906</v>
+        <v>0.07564722880598501</v>
       </c>
       <c r="C80">
-        <v>16.92404748543196</v>
+        <v>16.52395542174909</v>
       </c>
       <c r="D80">
-        <v>61.11604748543197</v>
+        <v>61.2999554217491</v>
       </c>
       <c r="E80">
-        <v>14.95200000000001</v>
+        <v>15.53600000000001</v>
       </c>
       <c r="F80">
-        <v>45.55200000000001</v>
+        <v>46.13600000000001</v>
       </c>
       <c r="G80">
         <v>1.36</v>
@@ -7847,28 +7847,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M80">
-        <v>2.919883200000001</v>
+        <v>2.957317600000001</v>
       </c>
       <c r="N80">
-        <v>5.973450133333333</v>
+        <v>5.936015733333333</v>
       </c>
       <c r="O80">
-        <v>1.612831536</v>
+        <v>1.602724248</v>
       </c>
       <c r="P80">
-        <v>4.360618597333334</v>
+        <v>4.333291485333334</v>
       </c>
       <c r="Q80">
-        <v>10.20061859733333</v>
+        <v>10.17329148533333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1783568358126845</v>
+        <v>0.1841940895523096</v>
       </c>
       <c r="T80">
-        <v>2.42782499994722</v>
+        <v>2.534736352147292</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.045783931813893</v>
+        <v>3.007229704828907</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07564722880598501</v>
+        <v>0.08011261373317942</v>
       </c>
       <c r="C81">
-        <v>16.52395542174909</v>
+        <v>7.962483955817611</v>
       </c>
       <c r="D81">
-        <v>61.2999554217491</v>
+        <v>53.32248395581762</v>
       </c>
       <c r="E81">
-        <v>15.53600000000001</v>
+        <v>16.12</v>
       </c>
       <c r="F81">
-        <v>46.13600000000001</v>
+        <v>46.72000000000001</v>
       </c>
       <c r="G81">
         <v>1.36</v>
@@ -7929,45 +7929,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M81">
-        <v>2.957317600000001</v>
+        <v>3.359168000000001</v>
       </c>
       <c r="N81">
-        <v>5.936015733333333</v>
+        <v>5.534165333333334</v>
       </c>
       <c r="O81">
-        <v>1.602724248</v>
+        <v>1.49422464</v>
       </c>
       <c r="P81">
-        <v>4.333291485333334</v>
+        <v>4.039940693333333</v>
       </c>
       <c r="Q81">
-        <v>10.17329148533333</v>
+        <v>9.879940693333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1841940895523096</v>
+        <v>0.1906150686658971</v>
       </c>
       <c r="T81">
-        <v>2.534736352147292</v>
+        <v>2.652338839567371</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.007229704828907</v>
+        <v>2.647480963540178</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08011261373317942</v>
+        <v>0.08007973866037382</v>
       </c>
       <c r="C82">
-        <v>7.962483955817611</v>
+        <v>7.429621467675283</v>
       </c>
       <c r="D82">
-        <v>53.32248395581762</v>
+        <v>53.37362146767529</v>
       </c>
       <c r="E82">
-        <v>16.12</v>
+        <v>16.70400000000001</v>
       </c>
       <c r="F82">
-        <v>46.72000000000001</v>
+        <v>47.30400000000001</v>
       </c>
       <c r="G82">
         <v>1.36</v>
@@ -8011,28 +8011,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M82">
-        <v>3.359168000000001</v>
+        <v>3.401157600000001</v>
       </c>
       <c r="N82">
-        <v>5.534165333333334</v>
+        <v>5.492175733333333</v>
       </c>
       <c r="O82">
-        <v>1.49422464</v>
+        <v>1.482887448</v>
       </c>
       <c r="P82">
-        <v>4.039940693333333</v>
+        <v>4.009288285333334</v>
       </c>
       <c r="Q82">
-        <v>9.879940693333333</v>
+        <v>9.849288285333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1906150686658971</v>
+        <v>0.197711940317757</v>
       </c>
       <c r="T82">
-        <v>2.652338839567371</v>
+        <v>2.782320536189564</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.647480963540178</v>
+        <v>2.614796013373015</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08007973866037382</v>
+        <v>0.08004686358756824</v>
       </c>
       <c r="C83">
-        <v>7.429621467675283</v>
+        <v>6.896857157833033</v>
       </c>
       <c r="D83">
-        <v>53.37362146767529</v>
+        <v>53.42485715783304</v>
       </c>
       <c r="E83">
-        <v>16.70400000000001</v>
+        <v>17.288</v>
       </c>
       <c r="F83">
-        <v>47.30400000000001</v>
+        <v>47.88800000000001</v>
       </c>
       <c r="G83">
         <v>1.36</v>
@@ -8093,28 +8093,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M83">
-        <v>3.401157600000001</v>
+        <v>3.443147200000001</v>
       </c>
       <c r="N83">
-        <v>5.492175733333333</v>
+        <v>5.450186133333334</v>
       </c>
       <c r="O83">
-        <v>1.482887448</v>
+        <v>1.471550256</v>
       </c>
       <c r="P83">
-        <v>4.009288285333334</v>
+        <v>3.978635877333334</v>
       </c>
       <c r="Q83">
-        <v>9.849288285333333</v>
+        <v>9.818635877333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.197711940317757</v>
+        <v>0.205597353264268</v>
       </c>
       <c r="T83">
-        <v>2.782320536189564</v>
+        <v>2.926744643547556</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.614796013373015</v>
+        <v>2.582908257112369</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08004686358756824</v>
+        <v>0.08001398851476264</v>
       </c>
       <c r="C84">
-        <v>6.896857157833033</v>
+        <v>6.364191309299606</v>
       </c>
       <c r="D84">
-        <v>53.42485715783304</v>
+        <v>53.47619130929962</v>
       </c>
       <c r="E84">
-        <v>17.288</v>
+        <v>17.87200000000001</v>
       </c>
       <c r="F84">
-        <v>47.88800000000001</v>
+        <v>48.47200000000001</v>
       </c>
       <c r="G84">
         <v>1.36</v>
@@ -8175,28 +8175,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M84">
-        <v>3.443147200000001</v>
+        <v>3.485136800000001</v>
       </c>
       <c r="N84">
-        <v>5.450186133333334</v>
+        <v>5.408196533333333</v>
       </c>
       <c r="O84">
-        <v>1.471550256</v>
+        <v>1.460213064</v>
       </c>
       <c r="P84">
-        <v>3.978635877333334</v>
+        <v>3.947983469333333</v>
       </c>
       <c r="Q84">
-        <v>9.818635877333334</v>
+        <v>9.787983469333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.205597353264268</v>
+        <v>0.214410461851545</v>
       </c>
       <c r="T84">
-        <v>2.926744643547556</v>
+        <v>3.08815982235943</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.582908257112369</v>
+        <v>2.551788880520653</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08001398851476264</v>
+        <v>0.07998111344195705</v>
       </c>
       <c r="C85">
-        <v>6.364191309299606</v>
+        <v>5.831624206172449</v>
       </c>
       <c r="D85">
-        <v>53.47619130929962</v>
+        <v>53.52762420617246</v>
       </c>
       <c r="E85">
-        <v>17.87200000000001</v>
+        <v>18.45600000000001</v>
       </c>
       <c r="F85">
-        <v>48.47200000000001</v>
+        <v>49.05600000000001</v>
       </c>
       <c r="G85">
         <v>1.36</v>
@@ -8257,28 +8257,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M85">
-        <v>3.485136800000001</v>
+        <v>3.527126400000001</v>
       </c>
       <c r="N85">
-        <v>5.408196533333333</v>
+        <v>5.366206933333333</v>
       </c>
       <c r="O85">
-        <v>1.460213064</v>
+        <v>1.448875872</v>
       </c>
       <c r="P85">
-        <v>3.947983469333333</v>
+        <v>3.917331061333333</v>
       </c>
       <c r="Q85">
-        <v>9.787983469333334</v>
+        <v>9.757331061333332</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.214410461851545</v>
+        <v>0.2243252090122317</v>
       </c>
       <c r="T85">
-        <v>3.08815982235943</v>
+        <v>3.269751898522788</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.551788880520653</v>
+        <v>2.521410441466836</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07998111344195705</v>
+        <v>0.08236818836915144</v>
       </c>
       <c r="C86">
-        <v>5.831624206172457</v>
+        <v>1.753482019937515</v>
       </c>
       <c r="D86">
-        <v>53.52762420617246</v>
+        <v>50.03348201993752</v>
       </c>
       <c r="E86">
-        <v>18.456</v>
+        <v>19.04</v>
       </c>
       <c r="F86">
-        <v>49.056</v>
+        <v>49.64</v>
       </c>
       <c r="G86">
         <v>1.36</v>
@@ -8339,45 +8339,45 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M86">
-        <v>3.527126400000001</v>
+        <v>3.762712000000001</v>
       </c>
       <c r="N86">
-        <v>5.366206933333334</v>
+        <v>5.130621333333334</v>
       </c>
       <c r="O86">
-        <v>1.448875872</v>
+        <v>1.38526776</v>
       </c>
       <c r="P86">
-        <v>3.917331061333334</v>
+        <v>3.745353573333333</v>
       </c>
       <c r="Q86">
-        <v>9.757331061333334</v>
+        <v>9.585353573333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2243252090122315</v>
+        <v>0.2355619224610097</v>
       </c>
       <c r="T86">
-        <v>3.269751898522786</v>
+        <v>3.475556251507923</v>
       </c>
       <c r="U86">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.521410441466836</v>
+        <v>2.363543458370806</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08236818836915144</v>
+        <v>0.08236378329634586</v>
       </c>
       <c r="C87">
-        <v>1.753482019937515</v>
+        <v>1.175509873489432</v>
       </c>
       <c r="D87">
-        <v>50.03348201993752</v>
+        <v>50.03950987348944</v>
       </c>
       <c r="E87">
-        <v>19.04</v>
+        <v>19.624</v>
       </c>
       <c r="F87">
-        <v>49.64</v>
+        <v>50.224</v>
       </c>
       <c r="G87">
         <v>1.36</v>
@@ -8421,28 +8421,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M87">
-        <v>3.762712000000001</v>
+        <v>3.806979200000001</v>
       </c>
       <c r="N87">
-        <v>5.130621333333334</v>
+        <v>5.086354133333334</v>
       </c>
       <c r="O87">
-        <v>1.38526776</v>
+        <v>1.373315616</v>
       </c>
       <c r="P87">
-        <v>3.745353573333333</v>
+        <v>3.713038517333334</v>
       </c>
       <c r="Q87">
-        <v>9.585353573333332</v>
+        <v>9.553038517333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2355619224610097</v>
+        <v>0.2484038806881847</v>
       </c>
       <c r="T87">
-        <v>3.475556251507923</v>
+        <v>3.710761226348082</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.363543458370806</v>
+        <v>2.336060394901378</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08236378329634586</v>
+        <v>0.08235937822354027</v>
       </c>
       <c r="C88">
-        <v>1.175509873489432</v>
+        <v>0.5975391796445066</v>
       </c>
       <c r="D88">
-        <v>50.03950987348944</v>
+        <v>50.04553917964451</v>
       </c>
       <c r="E88">
-        <v>19.624</v>
+        <v>20.20800000000001</v>
       </c>
       <c r="F88">
-        <v>50.224</v>
+        <v>50.80800000000001</v>
       </c>
       <c r="G88">
         <v>1.36</v>
@@ -8503,28 +8503,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M88">
-        <v>3.806979200000001</v>
+        <v>3.851246400000001</v>
       </c>
       <c r="N88">
-        <v>5.086354133333334</v>
+        <v>5.042086933333334</v>
       </c>
       <c r="O88">
-        <v>1.373315616</v>
+        <v>1.361363472</v>
       </c>
       <c r="P88">
-        <v>3.713038517333334</v>
+        <v>3.680723461333334</v>
       </c>
       <c r="Q88">
-        <v>9.553038517333334</v>
+        <v>9.520723461333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2484038806881847</v>
+        <v>0.2632215247964635</v>
       </c>
       <c r="T88">
-        <v>3.710761226348082</v>
+        <v>3.982151581932879</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.336060394901378</v>
+        <v>2.309209125994466</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08235937822354027</v>
+        <v>0.08235497315073467</v>
       </c>
       <c r="C89">
-        <v>0.5975391796445066</v>
+        <v>0.01956993892786585</v>
       </c>
       <c r="D89">
-        <v>50.04553917964451</v>
+        <v>50.05156993892787</v>
       </c>
       <c r="E89">
-        <v>20.20800000000001</v>
+        <v>20.792</v>
       </c>
       <c r="F89">
-        <v>50.80800000000001</v>
+        <v>51.392</v>
       </c>
       <c r="G89">
         <v>1.36</v>
@@ -8585,28 +8585,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M89">
-        <v>3.851246400000001</v>
+        <v>3.895513600000001</v>
       </c>
       <c r="N89">
-        <v>5.042086933333334</v>
+        <v>4.997819733333333</v>
       </c>
       <c r="O89">
-        <v>1.361363472</v>
+        <v>1.349411328</v>
       </c>
       <c r="P89">
-        <v>3.680723461333334</v>
+        <v>3.648408405333333</v>
       </c>
       <c r="Q89">
-        <v>9.520723461333333</v>
+        <v>9.488408405333333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2632215247964635</v>
+        <v>0.2805087762561223</v>
       </c>
       <c r="T89">
-        <v>3.982151581932879</v>
+        <v>4.298773663448477</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.309209125994466</v>
+        <v>2.282968113199074</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08235497315073467</v>
+        <v>0.08235056807792909</v>
       </c>
       <c r="C90">
-        <v>0.01956993892786585</v>
+        <v>-0.5583978481351295</v>
       </c>
       <c r="D90">
-        <v>50.05156993892787</v>
+        <v>50.05760215186488</v>
       </c>
       <c r="E90">
-        <v>20.792</v>
+        <v>21.376</v>
       </c>
       <c r="F90">
-        <v>51.392</v>
+        <v>51.97600000000001</v>
       </c>
       <c r="G90">
         <v>1.36</v>
@@ -8667,28 +8667,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M90">
-        <v>3.895513600000001</v>
+        <v>3.939780800000001</v>
       </c>
       <c r="N90">
-        <v>4.997819733333333</v>
+        <v>4.953552533333333</v>
       </c>
       <c r="O90">
-        <v>1.349411328</v>
+        <v>1.337459184</v>
       </c>
       <c r="P90">
-        <v>3.648408405333333</v>
+        <v>3.616093349333333</v>
       </c>
       <c r="Q90">
-        <v>9.488408405333333</v>
+        <v>9.456093349333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2805087762561223</v>
+        <v>0.3009391643448099</v>
       </c>
       <c r="T90">
-        <v>4.298773663448477</v>
+        <v>4.672963396148729</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.282968113199074</v>
+        <v>2.257316786084478</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08235056807792909</v>
+        <v>0.08234616300512348</v>
       </c>
       <c r="C91">
-        <v>-0.5583978481351295</v>
+        <v>-1.136364181018777</v>
       </c>
       <c r="D91">
-        <v>50.05760215186488</v>
+        <v>50.06363581898123</v>
       </c>
       <c r="E91">
-        <v>21.376</v>
+        <v>21.96000000000001</v>
       </c>
       <c r="F91">
-        <v>51.97600000000001</v>
+        <v>52.56000000000001</v>
       </c>
       <c r="G91">
         <v>1.36</v>
@@ -8749,28 +8749,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M91">
-        <v>3.939780800000001</v>
+        <v>3.984048000000001</v>
       </c>
       <c r="N91">
-        <v>4.953552533333333</v>
+        <v>4.909285333333333</v>
       </c>
       <c r="O91">
-        <v>1.337459184</v>
+        <v>1.32550704</v>
       </c>
       <c r="P91">
-        <v>3.616093349333333</v>
+        <v>3.583778293333333</v>
       </c>
       <c r="Q91">
-        <v>9.456093349333333</v>
+        <v>9.423778293333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3009391643448099</v>
+        <v>0.325455630051235</v>
       </c>
       <c r="T91">
-        <v>4.672963396148729</v>
+        <v>5.121991075389031</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.257316786084478</v>
+        <v>2.232235488461317</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08234616300512348</v>
+        <v>0.0823417579323179</v>
       </c>
       <c r="C92">
-        <v>-1.136364181018777</v>
+        <v>-1.714329059197233</v>
       </c>
       <c r="D92">
-        <v>50.06363581898123</v>
+        <v>50.06967094080277</v>
       </c>
       <c r="E92">
-        <v>21.96000000000001</v>
+        <v>22.544</v>
       </c>
       <c r="F92">
-        <v>52.56000000000001</v>
+        <v>53.14400000000001</v>
       </c>
       <c r="G92">
         <v>1.36</v>
@@ -8831,28 +8831,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M92">
-        <v>3.984048000000001</v>
+        <v>4.028315200000001</v>
       </c>
       <c r="N92">
-        <v>4.909285333333333</v>
+        <v>4.865018133333334</v>
       </c>
       <c r="O92">
-        <v>1.32550704</v>
+        <v>1.313554896</v>
       </c>
       <c r="P92">
-        <v>3.583778293333333</v>
+        <v>3.551463237333333</v>
       </c>
       <c r="Q92">
-        <v>9.423778293333333</v>
+        <v>9.391463237333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.325455630051235</v>
+        <v>0.3554201992479767</v>
       </c>
       <c r="T92">
-        <v>5.121991075389031</v>
+        <v>5.670802683349401</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.232235488461317</v>
+        <v>2.207705428148556</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0823417579323179</v>
+        <v>0.08233735285951231</v>
       </c>
       <c r="C93">
-        <v>-1.714329059197233</v>
+        <v>-2.292292482144319</v>
       </c>
       <c r="D93">
-        <v>50.06967094080277</v>
+        <v>50.07570751785569</v>
       </c>
       <c r="E93">
-        <v>22.544</v>
+        <v>23.12800000000001</v>
       </c>
       <c r="F93">
-        <v>53.14400000000001</v>
+        <v>53.72800000000001</v>
       </c>
       <c r="G93">
         <v>1.36</v>
@@ -8913,28 +8913,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M93">
-        <v>4.028315200000001</v>
+        <v>4.072582400000001</v>
       </c>
       <c r="N93">
-        <v>4.865018133333334</v>
+        <v>4.820750933333334</v>
       </c>
       <c r="O93">
-        <v>1.313554896</v>
+        <v>1.301602752</v>
       </c>
       <c r="P93">
-        <v>3.551463237333333</v>
+        <v>3.519148181333334</v>
       </c>
       <c r="Q93">
-        <v>9.391463237333333</v>
+        <v>9.359148181333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3554201992479767</v>
+        <v>0.392875910743904</v>
       </c>
       <c r="T93">
-        <v>5.670802683349401</v>
+        <v>6.356817193299864</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.207705428148556</v>
+        <v>2.183708630016506</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08233735285951231</v>
+        <v>0.08233294778670672</v>
       </c>
       <c r="C94">
-        <v>-2.292292482144319</v>
+        <v>-2.870254449333608</v>
       </c>
       <c r="D94">
-        <v>50.07570751785569</v>
+        <v>50.0817455506664</v>
       </c>
       <c r="E94">
-        <v>23.12800000000001</v>
+        <v>23.712</v>
       </c>
       <c r="F94">
-        <v>53.72800000000001</v>
+        <v>54.312</v>
       </c>
       <c r="G94">
         <v>1.36</v>
@@ -8995,28 +8995,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M94">
-        <v>4.072582400000001</v>
+        <v>4.116849600000001</v>
       </c>
       <c r="N94">
-        <v>4.820750933333334</v>
+        <v>4.776483733333333</v>
       </c>
       <c r="O94">
-        <v>1.301602752</v>
+        <v>1.289650608</v>
       </c>
       <c r="P94">
-        <v>3.519148181333334</v>
+        <v>3.486833125333333</v>
       </c>
       <c r="Q94">
-        <v>9.359148181333333</v>
+        <v>9.326833125333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.392875910743904</v>
+        <v>0.4410332540958105</v>
       </c>
       <c r="T94">
-        <v>6.356817193299864</v>
+        <v>7.238835848950457</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.183708630016506</v>
+        <v>2.160227892059339</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08233294778670672</v>
+        <v>0.08232854271390112</v>
       </c>
       <c r="C95">
-        <v>-2.870254449333608</v>
+        <v>-3.448214960238474</v>
       </c>
       <c r="D95">
-        <v>50.0817455506664</v>
+        <v>50.08778503976153</v>
       </c>
       <c r="E95">
-        <v>23.712</v>
+        <v>24.29600000000001</v>
       </c>
       <c r="F95">
-        <v>54.312</v>
+        <v>54.89600000000001</v>
       </c>
       <c r="G95">
         <v>1.36</v>
@@ -9077,28 +9077,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M95">
-        <v>4.116849600000001</v>
+        <v>4.161116800000001</v>
       </c>
       <c r="N95">
-        <v>4.776483733333333</v>
+        <v>4.732216533333333</v>
       </c>
       <c r="O95">
-        <v>1.289650608</v>
+        <v>1.277698464</v>
       </c>
       <c r="P95">
-        <v>3.486833125333333</v>
+        <v>3.454518069333333</v>
       </c>
       <c r="Q95">
-        <v>9.326833125333334</v>
+        <v>9.294518069333332</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4410332540958105</v>
+        <v>0.5052430452316857</v>
       </c>
       <c r="T95">
-        <v>7.238835848950457</v>
+        <v>8.41486072315125</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.160227892059339</v>
+        <v>2.137246744271474</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08232854271390112</v>
+        <v>0.08232413764109553</v>
       </c>
       <c r="C96">
-        <v>-3.448214960238474</v>
+        <v>-4.026174014331986</v>
       </c>
       <c r="D96">
-        <v>50.08778503976153</v>
+        <v>50.09382598566803</v>
       </c>
       <c r="E96">
-        <v>24.29600000000001</v>
+        <v>24.88000000000001</v>
       </c>
       <c r="F96">
-        <v>54.89600000000001</v>
+        <v>55.48000000000001</v>
       </c>
       <c r="G96">
         <v>1.36</v>
@@ -9159,28 +9159,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M96">
-        <v>4.161116800000001</v>
+        <v>4.205384000000001</v>
       </c>
       <c r="N96">
-        <v>4.732216533333333</v>
+        <v>4.687949333333333</v>
       </c>
       <c r="O96">
-        <v>1.277698464</v>
+        <v>1.26574632</v>
       </c>
       <c r="P96">
-        <v>3.454518069333333</v>
+        <v>3.422203013333333</v>
       </c>
       <c r="Q96">
-        <v>9.294518069333332</v>
+        <v>9.262203013333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5052430452316857</v>
+        <v>0.5951367528219114</v>
       </c>
       <c r="T96">
-        <v>8.41486072315125</v>
+        <v>10.06129554703236</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.137246744271474</v>
+        <v>2.114749410121247</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08232413764109553</v>
+        <v>0.08231973256828992</v>
       </c>
       <c r="C97">
-        <v>-4.026174014331986</v>
+        <v>-4.604131611086949</v>
       </c>
       <c r="D97">
-        <v>50.09382598566803</v>
+        <v>50.09986838891306</v>
       </c>
       <c r="E97">
-        <v>24.88000000000001</v>
+        <v>25.46400000000001</v>
       </c>
       <c r="F97">
-        <v>55.48000000000001</v>
+        <v>56.06400000000001</v>
       </c>
       <c r="G97">
         <v>1.36</v>
@@ -9241,28 +9241,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M97">
-        <v>4.205384000000001</v>
+        <v>4.249651200000001</v>
       </c>
       <c r="N97">
-        <v>4.687949333333333</v>
+        <v>4.643682133333334</v>
       </c>
       <c r="O97">
-        <v>1.26574632</v>
+        <v>1.253794176</v>
       </c>
       <c r="P97">
-        <v>3.422203013333333</v>
+        <v>3.389887957333333</v>
       </c>
       <c r="Q97">
-        <v>9.262203013333334</v>
+        <v>9.229887957333332</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5951367528219114</v>
+        <v>0.7299773142072495</v>
       </c>
       <c r="T97">
-        <v>10.06129554703236</v>
+        <v>12.53094778285403</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.114749410121247</v>
+        <v>2.092720770432485</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08231973256828994</v>
+        <v>0.08231532749548434</v>
       </c>
       <c r="C98">
-        <v>-4.604131611086963</v>
+        <v>-5.182087749976013</v>
       </c>
       <c r="D98">
-        <v>50.09986838891304</v>
+        <v>50.10591225002399</v>
       </c>
       <c r="E98">
-        <v>25.464</v>
+        <v>26.048</v>
       </c>
       <c r="F98">
-        <v>56.064</v>
+        <v>56.648</v>
       </c>
       <c r="G98">
         <v>1.36</v>
@@ -9323,28 +9323,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M98">
-        <v>4.249651200000001</v>
+        <v>4.293918400000001</v>
       </c>
       <c r="N98">
-        <v>4.643682133333334</v>
+        <v>4.599414933333334</v>
       </c>
       <c r="O98">
-        <v>1.253794176</v>
+        <v>1.241842032</v>
       </c>
       <c r="P98">
-        <v>3.389887957333333</v>
+        <v>3.357572901333334</v>
       </c>
       <c r="Q98">
-        <v>9.229887957333332</v>
+        <v>9.197572901333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7299773142072478</v>
+        <v>0.9547115831828107</v>
       </c>
       <c r="T98">
-        <v>12.530947782854</v>
+        <v>16.64703484255676</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.092720770432485</v>
+        <v>2.071146329500191</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08231532749548434</v>
+        <v>0.08231092242267876</v>
       </c>
       <c r="C99">
-        <v>-5.182087749976013</v>
+        <v>-5.760042430471451</v>
       </c>
       <c r="D99">
-        <v>50.10591225002399</v>
+        <v>50.11195756952856</v>
       </c>
       <c r="E99">
-        <v>26.048</v>
+        <v>26.63200000000001</v>
       </c>
       <c r="F99">
-        <v>56.648</v>
+        <v>57.23200000000001</v>
       </c>
       <c r="G99">
         <v>1.36</v>
@@ -9405,28 +9405,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M99">
-        <v>4.293918400000001</v>
+        <v>4.338185600000001</v>
       </c>
       <c r="N99">
-        <v>4.599414933333334</v>
+        <v>4.555147733333333</v>
       </c>
       <c r="O99">
-        <v>1.241842032</v>
+        <v>1.229889888</v>
       </c>
       <c r="P99">
-        <v>3.357572901333334</v>
+        <v>3.325257845333333</v>
       </c>
       <c r="Q99">
-        <v>9.197572901333334</v>
+        <v>9.165257845333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9547115831828107</v>
+        <v>1.404180121133936</v>
       </c>
       <c r="T99">
-        <v>16.64703484255676</v>
+        <v>24.87920896196228</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.071146329500191</v>
+        <v>2.050012183280801</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08231092242267876</v>
+        <v>0.08230651734987315</v>
       </c>
       <c r="C100">
-        <v>-5.760042430471451</v>
+        <v>-6.337995652045294</v>
       </c>
       <c r="D100">
-        <v>50.11195756952856</v>
+        <v>50.11800434795471</v>
       </c>
       <c r="E100">
-        <v>26.63200000000001</v>
+        <v>27.216</v>
       </c>
       <c r="F100">
-        <v>57.23200000000001</v>
+        <v>57.816</v>
       </c>
       <c r="G100">
         <v>1.36</v>
@@ -9487,28 +9487,28 @@
         <v>8.893333333333334</v>
       </c>
       <c r="M100">
-        <v>4.338185600000001</v>
+        <v>4.3824528</v>
       </c>
       <c r="N100">
-        <v>4.555147733333333</v>
+        <v>4.510880533333334</v>
       </c>
       <c r="O100">
-        <v>1.229889888</v>
+        <v>1.217937744</v>
       </c>
       <c r="P100">
-        <v>3.325257845333333</v>
+        <v>3.292942789333334</v>
       </c>
       <c r="Q100">
-        <v>9.165257845333333</v>
+        <v>9.132942789333335</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.404180121133936</v>
+        <v>2.752585734987314</v>
       </c>
       <c r="T100">
-        <v>24.87920896196228</v>
+        <v>49.57573132017886</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.050012183280801</v>
+        <v>2.029304989510289</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08230651734987315</v>
-      </c>
-      <c r="C101">
-        <v>-6.337995652045294</v>
-      </c>
-      <c r="D101">
-        <v>50.11800434795471</v>
-      </c>
-      <c r="E101">
-        <v>27.216</v>
-      </c>
-      <c r="F101">
-        <v>57.816</v>
-      </c>
-      <c r="G101">
-        <v>1.36</v>
-      </c>
-      <c r="H101">
-        <v>27.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.73333333333333</v>
-      </c>
-      <c r="K101">
-        <v>5.84</v>
-      </c>
-      <c r="L101">
-        <v>8.893333333333334</v>
-      </c>
-      <c r="M101">
-        <v>4.3824528</v>
-      </c>
-      <c r="N101">
-        <v>4.510880533333334</v>
-      </c>
-      <c r="O101">
-        <v>1.217937744</v>
-      </c>
-      <c r="P101">
-        <v>3.292942789333334</v>
-      </c>
-      <c r="Q101">
-        <v>9.132942789333335</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.752585734987314</v>
-      </c>
-      <c r="T101">
-        <v>49.57573132017886</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.055334</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.029304989510289</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
